--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,10 @@
     <font>
       <name val="Arial"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -41,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,14 +53,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R251"/>
+  <dimension ref="A1:R351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -19521,6 +19542,7106 @@
         </is>
       </c>
     </row>
+    <row r="252" ht="60" customHeight="1">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>EX-0251</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr"/>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>Let me set the stage before we dive in.</t>
+        </is>
+      </c>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>本題に入る前に、背景・前提を説明させてください、という導入表現。</t>
+        </is>
+      </c>
+      <c r="I252" s="3" t="inlineStr">
+        <is>
+          <t>Let me set the stage before we dive in — this project started six months ago.</t>
+        </is>
+      </c>
+      <c r="J252" s="3" t="inlineStr">
+        <is>
+          <t>本題に入る前に背景を説明させてください。このプロジェクトは半年前に始まりました。</t>
+        </is>
+      </c>
+      <c r="K252" s="3" t="n"/>
+      <c r="L252" s="3" t="n"/>
+      <c r="M252" s="3" t="inlineStr"/>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
+          <t>「set the stage」は演劇用語由来で「舞台を整える」＝前提を共有する意味。</t>
+        </is>
+      </c>
+      <c r="O252" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P252" s="3" t="inlineStr"/>
+      <c r="Q252" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R252" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="60" customHeight="1">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>EX-0252</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr"/>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>I'll keep the slides light on text.</t>
+        </is>
+      </c>
+      <c r="H253" s="3" t="inlineStr">
+        <is>
+          <t>スライドの文字は少なめにしています、という進行上の一言。</t>
+        </is>
+      </c>
+      <c r="I253" s="3" t="inlineStr">
+        <is>
+          <t>I'll keep the slides light on text so we can focus on the discussion.</t>
+        </is>
+      </c>
+      <c r="J253" s="3" t="inlineStr">
+        <is>
+          <t>議論に集中できるよう、スライドの文字は少なめにしています。</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="n"/>
+      <c r="L253" s="3" t="n"/>
+      <c r="M253" s="3" t="inlineStr"/>
+      <c r="N253" s="3" t="inlineStr"/>
+      <c r="O253" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P253" s="3" t="inlineStr"/>
+      <c r="Q253" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R253" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="60" customHeight="1">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>EX-0253</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr"/>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>Let's fast-forward to the results.</t>
+        </is>
+      </c>
+      <c r="H254" s="3" t="inlineStr">
+        <is>
+          <t>結果まで話を進めましょう、という意味。プロセスを省略して結論に移るときに使う。</t>
+        </is>
+      </c>
+      <c r="I254" s="3" t="inlineStr">
+        <is>
+          <t>I'll skip the methodology and fast-forward to the results.</t>
+        </is>
+      </c>
+      <c r="J254" s="3" t="inlineStr">
+        <is>
+          <t>手法の説明は飛ばして、結果まで話を進めます。</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="n"/>
+      <c r="L254" s="3" t="n"/>
+      <c r="M254" s="3" t="inlineStr"/>
+      <c r="N254" s="3" t="inlineStr"/>
+      <c r="O254" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P254" s="3" t="inlineStr"/>
+      <c r="Q254" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R254" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="60" customHeight="1">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>EX-0254</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr"/>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>I'll pause here for any questions.</t>
+        </is>
+      </c>
+      <c r="H255" s="3" t="inlineStr">
+        <is>
+          <t>ここで質問を受け付けます、というプレゼン中の区切りの表現。</t>
+        </is>
+      </c>
+      <c r="I255" s="3" t="inlineStr">
+        <is>
+          <t>I'll pause here for any questions before moving to the next section.</t>
+        </is>
+      </c>
+      <c r="J255" s="3" t="inlineStr">
+        <is>
+          <t>次のセクションに移る前に、ここで質問を受け付けます。</t>
+        </is>
+      </c>
+      <c r="K255" s="3" t="n"/>
+      <c r="L255" s="3" t="n"/>
+      <c r="M255" s="3" t="inlineStr"/>
+      <c r="N255" s="3" t="inlineStr"/>
+      <c r="O255" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P255" s="3" t="inlineStr"/>
+      <c r="Q255" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R255" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="60" customHeight="1">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>EX-0255</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr"/>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>To wrap things up, ...</t>
+        </is>
+      </c>
+      <c r="H256" s="3" t="inlineStr">
+        <is>
+          <t>まとめると、という話をまとめる際の定型句。</t>
+        </is>
+      </c>
+      <c r="I256" s="3" t="inlineStr">
+        <is>
+          <t>To wrap things up, we're on track to hit our Q3 targets.</t>
+        </is>
+      </c>
+      <c r="J256" s="3" t="inlineStr">
+        <is>
+          <t>まとめると、Q3の目標達成に向けて順調に進んでいます。</t>
+        </is>
+      </c>
+      <c r="K256" s="3" t="n"/>
+      <c r="L256" s="3" t="n"/>
+      <c r="M256" s="3" t="inlineStr"/>
+      <c r="N256" s="3" t="inlineStr"/>
+      <c r="O256" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P256" s="3" t="inlineStr"/>
+      <c r="Q256" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R256" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="60" customHeight="1">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>EX-0256</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr"/>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>Let me back up for a second.</t>
+        </is>
+      </c>
+      <c r="H257" s="3" t="inlineStr">
+        <is>
+          <t>少し話を戻します、という意味。説明が前後したり補足が必要なときに使う。</t>
+        </is>
+      </c>
+      <c r="I257" s="3" t="inlineStr">
+        <is>
+          <t>Let me back up for a second — I should explain why this matters first.</t>
+        </is>
+      </c>
+      <c r="J257" s="3" t="inlineStr">
+        <is>
+          <t>少し話を戻しますが、まずこれが重要な理由を説明すべきでした。</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="n"/>
+      <c r="L257" s="3" t="n"/>
+      <c r="M257" s="3" t="inlineStr"/>
+      <c r="N257" s="3" t="inlineStr"/>
+      <c r="O257" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P257" s="3" t="inlineStr"/>
+      <c r="Q257" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R257" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="60" customHeight="1">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>EX-0257</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr"/>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>This slide speaks for itself.</t>
+        </is>
+      </c>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>このスライドを見れば一目瞭然です、という意味。データが説明を必要としないほど明確なときに使う。</t>
+        </is>
+      </c>
+      <c r="I258" s="3" t="inlineStr">
+        <is>
+          <t>This slide speaks for itself — engagement doubled after the redesign.</t>
+        </is>
+      </c>
+      <c r="J258" s="3" t="inlineStr">
+        <is>
+          <t>このスライドを見れば一目瞭然ですが、リニューアル後にエンゲージメントが倍増しました。</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="n"/>
+      <c r="L258" s="3" t="n"/>
+      <c r="M258" s="3" t="inlineStr"/>
+      <c r="N258" s="3" t="inlineStr"/>
+      <c r="O258" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P258" s="3" t="inlineStr"/>
+      <c r="Q258" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R258" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="60" customHeight="1">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>EX-0258</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr"/>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>I'll let the numbers do the talking.</t>
+        </is>
+      </c>
+      <c r="H259" s="3" t="inlineStr">
+        <is>
+          <t>数字が物語っています、という意味。データそのものに説得力を持たせる言い方。</t>
+        </is>
+      </c>
+      <c r="I259" s="3" t="inlineStr">
+        <is>
+          <t>Rather than convince you with words, I'll let the numbers do the talking.</t>
+        </is>
+      </c>
+      <c r="J259" s="3" t="inlineStr">
+        <is>
+          <t>言葉で説得するより、数字に語らせようと思います。</t>
+        </is>
+      </c>
+      <c r="K259" s="3" t="n"/>
+      <c r="L259" s="3" t="n"/>
+      <c r="M259" s="3" t="inlineStr"/>
+      <c r="N259" s="3" t="inlineStr"/>
+      <c r="O259" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P259" s="3" t="inlineStr"/>
+      <c r="Q259" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R259" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="60" customHeight="1">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>EX-0259</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr"/>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>Let's put this into context.</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>これを文脈の中で捉えてみましょう、という意味。単独の数字や事実の意味合いを説明する前置き。</t>
+        </is>
+      </c>
+      <c r="I260" s="3" t="inlineStr">
+        <is>
+          <t>Let's put this into context — a 5% drop sounds small, but it's our biggest market.</t>
+        </is>
+      </c>
+      <c r="J260" s="3" t="inlineStr">
+        <is>
+          <t>これを文脈の中で捉えると、5%の減少は小さく見えても、そこは最大の市場です。</t>
+        </is>
+      </c>
+      <c r="K260" s="3" t="n"/>
+      <c r="L260" s="3" t="n"/>
+      <c r="M260" s="3" t="inlineStr"/>
+      <c r="N260" s="3" t="inlineStr"/>
+      <c r="O260" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P260" s="3" t="inlineStr"/>
+      <c r="Q260" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R260" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="60" customHeight="1">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>EX-0260</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr"/>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>I'll skip ahead to slide 12.</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>スライド12まで飛ばします、という進行の指示。</t>
+        </is>
+      </c>
+      <c r="I261" s="3" t="inlineStr">
+        <is>
+          <t>In the interest of time, I'll skip ahead to slide 12.</t>
+        </is>
+      </c>
+      <c r="J261" s="3" t="inlineStr">
+        <is>
+          <t>時間の都合上、スライド12まで飛ばします。</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="n"/>
+      <c r="L261" s="3" t="n"/>
+      <c r="M261" s="3" t="inlineStr"/>
+      <c r="N261" s="3" t="inlineStr"/>
+      <c r="O261" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P261" s="3" t="inlineStr"/>
+      <c r="Q261" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R261" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="60" customHeight="1">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>EX-0261</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr"/>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>Feel free to save your questions for the end.</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>質問は最後にまとめてお願いします、という進行上のお願い。</t>
+        </is>
+      </c>
+      <c r="I262" s="3" t="inlineStr">
+        <is>
+          <t>Feel free to save your questions for the end — I'll cover a lot of this later.</t>
+        </is>
+      </c>
+      <c r="J262" s="3" t="inlineStr">
+        <is>
+          <t>質問は最後にまとめてお願いします。この点は後ほど詳しく触れます。</t>
+        </is>
+      </c>
+      <c r="K262" s="3" t="n"/>
+      <c r="L262" s="3" t="n"/>
+      <c r="M262" s="3" t="inlineStr"/>
+      <c r="N262" s="3" t="inlineStr"/>
+      <c r="O262" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P262" s="3" t="inlineStr"/>
+      <c r="Q262" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R262" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="60" customHeight="1">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>EX-0262</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr"/>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>Let me highlight the key takeaway here.</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="inlineStr">
+        <is>
+          <t>ここでの重要なポイントを強調させてください、という意味。</t>
+        </is>
+      </c>
+      <c r="I263" s="3" t="inlineStr">
+        <is>
+          <t>Let me highlight the key takeaway here: costs dropped by 20%.</t>
+        </is>
+      </c>
+      <c r="J263" s="3" t="inlineStr">
+        <is>
+          <t>ここでの重要なポイントを強調させてください。コストが20%下がりました。</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="n"/>
+      <c r="L263" s="3" t="n"/>
+      <c r="M263" s="3" t="inlineStr"/>
+      <c r="N263" s="3" t="inlineStr"/>
+      <c r="O263" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P263" s="3" t="inlineStr"/>
+      <c r="Q263" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R263" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="60" customHeight="1">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>EX-0263</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr"/>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>I want to draw your attention to this chart.</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>このグラフに注目していただきたいです、という意味。</t>
+        </is>
+      </c>
+      <c r="I264" s="3" t="inlineStr">
+        <is>
+          <t>I want to draw your attention to this chart — notice the spike in March.</t>
+        </is>
+      </c>
+      <c r="J264" s="3" t="inlineStr">
+        <is>
+          <t>このグラフに注目していただきたいのですが、3月の急増にご注目ください。</t>
+        </is>
+      </c>
+      <c r="K264" s="3" t="n"/>
+      <c r="L264" s="3" t="n"/>
+      <c r="M264" s="3" t="inlineStr"/>
+      <c r="N264" s="3" t="inlineStr"/>
+      <c r="O264" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P264" s="3" t="inlineStr"/>
+      <c r="Q264" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R264" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="60" customHeight="1">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>EX-0264</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr"/>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>That wraps up my presentation.</t>
+        </is>
+      </c>
+      <c r="H265" s="3" t="inlineStr">
+        <is>
+          <t>以上でプレゼンを終わります、という締めの表現。</t>
+        </is>
+      </c>
+      <c r="I265" s="3" t="inlineStr">
+        <is>
+          <t>That wraps up my presentation — happy to take any questions now.</t>
+        </is>
+      </c>
+      <c r="J265" s="3" t="inlineStr">
+        <is>
+          <t>以上でプレゼンを終わります。ここからご質問をお受けします。</t>
+        </is>
+      </c>
+      <c r="K265" s="3" t="n"/>
+      <c r="L265" s="3" t="n"/>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>That's all from me.</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr"/>
+      <c r="O265" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P265" s="3" t="inlineStr"/>
+      <c r="Q265" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R265" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="60" customHeight="1">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>EX-0265</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr"/>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>Let's open the floor for questions.</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>質疑応答に移りましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I266" s="3" t="inlineStr">
+        <is>
+          <t>Let's open the floor for questions — I'll do my best to answer everything.</t>
+        </is>
+      </c>
+      <c r="J266" s="3" t="inlineStr">
+        <is>
+          <t>質疑応答に移りましょう。できる限りお答えします。</t>
+        </is>
+      </c>
+      <c r="K266" s="3" t="n"/>
+      <c r="L266" s="3" t="n"/>
+      <c r="M266" s="3" t="inlineStr"/>
+      <c r="N266" s="3" t="inlineStr"/>
+      <c r="O266" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P266" s="3" t="inlineStr"/>
+      <c r="Q266" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R266" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="60" customHeight="1">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>EX-0266</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr"/>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>I'll try to keep this under ten minutes.</t>
+        </is>
+      </c>
+      <c r="H267" s="3" t="inlineStr">
+        <is>
+          <t>10分以内に収めるようにします、という時間配分への言及。</t>
+        </is>
+      </c>
+      <c r="I267" s="3" t="inlineStr">
+        <is>
+          <t>I'll try to keep this under ten minutes so we have time for discussion.</t>
+        </is>
+      </c>
+      <c r="J267" s="3" t="inlineStr">
+        <is>
+          <t>議論の時間を確保するため、10分以内に収めるようにします。</t>
+        </is>
+      </c>
+      <c r="K267" s="3" t="n"/>
+      <c r="L267" s="3" t="n"/>
+      <c r="M267" s="3" t="inlineStr"/>
+      <c r="N267" s="3" t="inlineStr"/>
+      <c r="O267" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P267" s="3" t="inlineStr"/>
+      <c r="Q267" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R267" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="60" customHeight="1">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>EX-0267</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr"/>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>This next part is where it gets interesting.</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>ここからが面白いところです、という関心を引く前置き。</t>
+        </is>
+      </c>
+      <c r="I268" s="3" t="inlineStr">
+        <is>
+          <t>This next part is where it gets interesting — the results surprised even us.</t>
+        </is>
+      </c>
+      <c r="J268" s="3" t="inlineStr">
+        <is>
+          <t>ここからが面白いところですが、結果は私たちも驚くものでした。</t>
+        </is>
+      </c>
+      <c r="K268" s="3" t="n"/>
+      <c r="L268" s="3" t="n"/>
+      <c r="M268" s="3" t="inlineStr"/>
+      <c r="N268" s="3" t="inlineStr"/>
+      <c r="O268" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P268" s="3" t="inlineStr"/>
+      <c r="Q268" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R268" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="60" customHeight="1">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>EX-0268</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>反論・懸念,確認</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>Let me address that head-on.</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>その点について正面からお答えします、という懸念や疑問に真正面から答える表現。</t>
+        </is>
+      </c>
+      <c r="I269" s="3" t="inlineStr">
+        <is>
+          <t>That's a fair concern — let me address that head-on.</t>
+        </is>
+      </c>
+      <c r="J269" s="3" t="inlineStr">
+        <is>
+          <t>もっともな懸念ですね。その点について正面からお答えします。</t>
+        </is>
+      </c>
+      <c r="K269" s="3" t="n"/>
+      <c r="L269" s="3" t="n"/>
+      <c r="M269" s="3" t="inlineStr"/>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
+          <t>質疑応答で厳しい質問が来たときに使える前向きな受け方。</t>
+        </is>
+      </c>
+      <c r="O269" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P269" s="3" t="inlineStr"/>
+      <c r="Q269" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R269" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="60" customHeight="1">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>EX-0269</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr"/>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>I'd like to preface this by saying...</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>前置きとして申し上げますと、という意味。本題の前に注意点や背景を伝える表現。</t>
+        </is>
+      </c>
+      <c r="I270" s="3" t="inlineStr">
+        <is>
+          <t>I'd like to preface this by saying these numbers are still preliminary.</t>
+        </is>
+      </c>
+      <c r="J270" s="3" t="inlineStr">
+        <is>
+          <t>前置きとして申し上げますと、この数字はまだ暫定的なものです。</t>
+        </is>
+      </c>
+      <c r="K270" s="3" t="n"/>
+      <c r="L270" s="3" t="n"/>
+      <c r="M270" s="3" t="inlineStr"/>
+      <c r="N270" s="3" t="inlineStr"/>
+      <c r="O270" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P270" s="3" t="inlineStr"/>
+      <c r="Q270" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R270" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="60" customHeight="1">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>EX-0270</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr"/>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>Let's revisit the agenda for a moment.</t>
+        </is>
+      </c>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>一旦アジェンダを確認しましょう、という進行の確認表現。</t>
+        </is>
+      </c>
+      <c r="I271" s="3" t="inlineStr">
+        <is>
+          <t>Let's revisit the agenda for a moment before we continue.</t>
+        </is>
+      </c>
+      <c r="J271" s="3" t="inlineStr">
+        <is>
+          <t>続ける前に、一旦アジェンダを確認しましょう。</t>
+        </is>
+      </c>
+      <c r="K271" s="3" t="n"/>
+      <c r="L271" s="3" t="n"/>
+      <c r="M271" s="3" t="inlineStr"/>
+      <c r="N271" s="3" t="inlineStr"/>
+      <c r="O271" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P271" s="3" t="inlineStr"/>
+      <c r="Q271" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R271" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="60" customHeight="1">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>EX-0271</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr"/>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>Let's keep this meeting tight.</t>
+        </is>
+      </c>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>このミーティングは手短にしましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I272" s="3" t="inlineStr">
+        <is>
+          <t>We have a lot to cover, so let's keep this meeting tight.</t>
+        </is>
+      </c>
+      <c r="J272" s="3" t="inlineStr">
+        <is>
+          <t>議題が多いので、このミーティングは手短にしましょう。</t>
+        </is>
+      </c>
+      <c r="K272" s="3" t="n"/>
+      <c r="L272" s="3" t="n"/>
+      <c r="M272" s="3" t="inlineStr"/>
+      <c r="N272" s="3" t="inlineStr"/>
+      <c r="O272" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P272" s="3" t="inlineStr"/>
+      <c r="Q272" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R272" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="60" customHeight="1">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>EX-0272</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>I want to make sure we leave with clear action items.</t>
+        </is>
+      </c>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>明確なアクションアイテムを持って終わりたいです、という意味。</t>
+        </is>
+      </c>
+      <c r="I273" s="3" t="inlineStr">
+        <is>
+          <t>I want to make sure we leave with clear action items today.</t>
+        </is>
+      </c>
+      <c r="J273" s="3" t="inlineStr">
+        <is>
+          <t>今日は明確なアクションアイテムを持って終わりたいです。</t>
+        </is>
+      </c>
+      <c r="K273" s="3" t="n"/>
+      <c r="L273" s="3" t="n"/>
+      <c r="M273" s="3" t="inlineStr"/>
+      <c r="N273" s="3" t="inlineStr"/>
+      <c r="O273" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P273" s="3" t="inlineStr"/>
+      <c r="Q273" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R273" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="60" customHeight="1">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>EX-0273</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>Who's taking notes for this one?</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>誰が議事録を取りますか、という進行上の確認。</t>
+        </is>
+      </c>
+      <c r="I274" s="3" t="inlineStr">
+        <is>
+          <t>Who's taking notes for this one? I can do it if no one else can.</t>
+        </is>
+      </c>
+      <c r="J274" s="3" t="inlineStr">
+        <is>
+          <t>誰が議事録を取りますか。他に誰もいなければ私がやります。</t>
+        </is>
+      </c>
+      <c r="K274" s="3" t="n"/>
+      <c r="L274" s="3" t="n"/>
+      <c r="M274" s="3" t="inlineStr"/>
+      <c r="N274" s="3" t="inlineStr"/>
+      <c r="O274" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P274" s="3" t="inlineStr"/>
+      <c r="Q274" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R274" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="60" customHeight="1">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>EX-0274</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>Let's assign owners to each action item.</t>
+        </is>
+      </c>
+      <c r="H275" s="3" t="inlineStr">
+        <is>
+          <t>各アクションアイテムに担当者を割り振りましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I275" s="3" t="inlineStr">
+        <is>
+          <t>Before we close, let's assign owners to each action item.</t>
+        </is>
+      </c>
+      <c r="J275" s="3" t="inlineStr">
+        <is>
+          <t>終わる前に、各アクションアイテムに担当者を割り振りましょう。</t>
+        </is>
+      </c>
+      <c r="K275" s="3" t="n"/>
+      <c r="L275" s="3" t="n"/>
+      <c r="M275" s="3" t="inlineStr"/>
+      <c r="N275" s="3" t="inlineStr"/>
+      <c r="O275" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P275" s="3" t="inlineStr"/>
+      <c r="Q275" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R275" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="60" customHeight="1">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>EX-0275</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>I think we're going in circles.</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>堂々巡りになっている気がします、という議論の停滞を指摘する表現。</t>
+        </is>
+      </c>
+      <c r="I276" s="3" t="inlineStr">
+        <is>
+          <t>I think we're going in circles — can we try a different approach?</t>
+        </is>
+      </c>
+      <c r="J276" s="3" t="inlineStr">
+        <is>
+          <t>堂々巡りになっている気がします。違うアプローチを試しませんか。</t>
+        </is>
+      </c>
+      <c r="K276" s="3" t="n"/>
+      <c r="L276" s="3" t="n"/>
+      <c r="M276" s="3" t="inlineStr"/>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
+          <t>率直だが対立的すぎない、議論の軌道修正を促す言い方。</t>
+        </is>
+      </c>
+      <c r="O276" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P276" s="3" t="inlineStr"/>
+      <c r="Q276" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R276" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="60" customHeight="1">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>EX-0276</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>Can we get everyone's buy-in before moving forward?</t>
+        </is>
+      </c>
+      <c r="H277" s="3" t="inlineStr">
+        <is>
+          <t>進める前に皆の同意を得られますか、という意味。</t>
+        </is>
+      </c>
+      <c r="I277" s="3" t="inlineStr">
+        <is>
+          <t>Can we get everyone's buy-in before moving forward with this plan?</t>
+        </is>
+      </c>
+      <c r="J277" s="3" t="inlineStr">
+        <is>
+          <t>この計画を進める前に、皆の同意を得られますか。</t>
+        </is>
+      </c>
+      <c r="K277" s="3" t="n"/>
+      <c r="L277" s="3" t="n"/>
+      <c r="M277" s="3" t="inlineStr"/>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
+          <t>「buy-in」は「賛同・納得」の意味でビジネスで頻出。</t>
+        </is>
+      </c>
+      <c r="O277" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P277" s="3" t="inlineStr"/>
+      <c r="Q277" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R277" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="60" customHeight="1">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>EX-0277</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr"/>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>Let's set a hard stop at the top of the hour.</t>
+        </is>
+      </c>
+      <c r="H278" s="3" t="inlineStr">
+        <is>
+          <t>ちょうど1時間で必ず終わらせましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I278" s="3" t="inlineStr">
+        <is>
+          <t>Let's set a hard stop at the top of the hour — I have another call after this.</t>
+        </is>
+      </c>
+      <c r="J278" s="3" t="inlineStr">
+        <is>
+          <t>ちょうど1時間で必ず終わらせましょう。この後別の電話があるので。</t>
+        </is>
+      </c>
+      <c r="K278" s="3" t="n"/>
+      <c r="L278" s="3" t="n"/>
+      <c r="M278" s="3" t="inlineStr"/>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
+          <t>「hard stop」は「絶対に動かせない終了時刻」の意味。</t>
+        </is>
+      </c>
+      <c r="O278" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P278" s="3" t="inlineStr"/>
+      <c r="Q278" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R278" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="60" customHeight="1">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>EX-0278</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>I want to flag a concern before we proceed.</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="inlineStr">
+        <is>
+          <t>進める前に懸念点を伝えたいです、という意味。</t>
+        </is>
+      </c>
+      <c r="I279" s="3" t="inlineStr">
+        <is>
+          <t>I want to flag a concern before we proceed with the launch.</t>
+        </is>
+      </c>
+      <c r="J279" s="3" t="inlineStr">
+        <is>
+          <t>ローンチを進める前に、懸念点を伝えたいです。</t>
+        </is>
+      </c>
+      <c r="K279" s="3" t="n"/>
+      <c r="L279" s="3" t="n"/>
+      <c r="M279" s="3" t="inlineStr"/>
+      <c r="N279" s="3" t="inlineStr"/>
+      <c r="O279" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P279" s="3" t="inlineStr"/>
+      <c r="Q279" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R279" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="60" customHeight="1">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>EX-0279</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>Let's not boil the ocean here.</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="inlineStr">
+        <is>
+          <t>あれもこれもやろうとしないようにしましょう、という意味。範囲を絞ろうという提案。</t>
+        </is>
+      </c>
+      <c r="I280" s="3" t="inlineStr">
+        <is>
+          <t>Let's not boil the ocean here — let's focus on the top three priorities.</t>
+        </is>
+      </c>
+      <c r="J280" s="3" t="inlineStr">
+        <is>
+          <t>あれもこれもやろうとせず、優先度の高い3つに絞りましょう。</t>
+        </is>
+      </c>
+      <c r="K280" s="3" t="n"/>
+      <c r="L280" s="3" t="n"/>
+      <c r="M280" s="3" t="inlineStr"/>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
+          <t>「boil the ocean」は「無謀に手を広げすぎる」という意味の慣用句。</t>
+        </is>
+      </c>
+      <c r="O280" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P280" s="3" t="inlineStr"/>
+      <c r="Q280" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R280" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="60" customHeight="1">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>EX-0280</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr"/>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>Can we do a quick round of introductions?</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="inlineStr">
+        <is>
+          <t>簡単に自己紹介をしましょうか、という意味。</t>
+        </is>
+      </c>
+      <c r="I281" s="3" t="inlineStr">
+        <is>
+          <t>Since we have new members, can we do a quick round of introductions?</t>
+        </is>
+      </c>
+      <c r="J281" s="3" t="inlineStr">
+        <is>
+          <t>新しいメンバーもいるので、簡単に自己紹介をしましょうか。</t>
+        </is>
+      </c>
+      <c r="K281" s="3" t="n"/>
+      <c r="L281" s="3" t="n"/>
+      <c r="M281" s="3" t="inlineStr"/>
+      <c r="N281" s="3" t="inlineStr"/>
+      <c r="O281" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P281" s="3" t="inlineStr"/>
+      <c r="Q281" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R281" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="60" customHeight="1">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>EX-0281</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>同意・肯定,相槌・共感</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>I'd like to build on what Sarah just said.</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>サラの発言に補足したいです、という意味。他者の意見に賛同しつつ発展させる表現。</t>
+        </is>
+      </c>
+      <c r="I282" s="3" t="inlineStr">
+        <is>
+          <t>I'd like to build on what Sarah just said about the timeline.</t>
+        </is>
+      </c>
+      <c r="J282" s="3" t="inlineStr">
+        <is>
+          <t>スケジュールについてのサラの発言に補足したいです。</t>
+        </is>
+      </c>
+      <c r="K282" s="3" t="n"/>
+      <c r="L282" s="3" t="n"/>
+      <c r="M282" s="3" t="inlineStr"/>
+      <c r="N282" s="3" t="inlineStr"/>
+      <c r="O282" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P282" s="3" t="inlineStr"/>
+      <c r="Q282" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R282" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="60" customHeight="1">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>EX-0282</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>That's a fair point, but I see it a bit differently.</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>一理ありますが、私は少し違う見方をしています、という丁寧な反論表現。</t>
+        </is>
+      </c>
+      <c r="I283" s="3" t="inlineStr">
+        <is>
+          <t>That's a fair point, but I see it a bit differently based on last quarter's data.</t>
+        </is>
+      </c>
+      <c r="J283" s="3" t="inlineStr">
+        <is>
+          <t>一理ありますが、前四半期のデータを踏まえると少し違う見方をしています。</t>
+        </is>
+      </c>
+      <c r="K283" s="3" t="n"/>
+      <c r="L283" s="3" t="n"/>
+      <c r="M283" s="3" t="inlineStr"/>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
+          <t>相手の意見を尊重しつつ反対意見を述べる、角の立たない言い方。</t>
+        </is>
+      </c>
+      <c r="O283" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P283" s="3" t="inlineStr"/>
+      <c r="Q283" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R283" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="60" customHeight="1">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>EX-0283</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>Let's not put the cart before the horse.</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>順序を間違えないようにしましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr">
+        <is>
+          <t>Let's not put the cart before the horse — we need approval before we start building.</t>
+        </is>
+      </c>
+      <c r="J284" s="3" t="inlineStr">
+        <is>
+          <t>順序を間違えないようにしましょう。着手する前に承認が必要です。</t>
+        </is>
+      </c>
+      <c r="K284" s="3" t="n"/>
+      <c r="L284" s="3" t="n"/>
+      <c r="M284" s="3" t="inlineStr"/>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
+          <t>「本末転倒にならないように」という定番の慣用句。</t>
+        </is>
+      </c>
+      <c r="O284" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P284" s="3" t="inlineStr"/>
+      <c r="Q284" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R284" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="60" customHeight="1">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>EX-0284</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>同意・肯定,相槌・共感</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>I second that.</t>
+        </is>
+      </c>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>私も同感です、という意味。誰かの意見に賛成を表明する表現。</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr">
+        <is>
+          <t>I second that — I think we should prioritize the client feedback first.</t>
+        </is>
+      </c>
+      <c r="J285" s="3" t="inlineStr">
+        <is>
+          <t>私も同感です。まずクライアントのフィードバックを優先すべきだと思います。</t>
+        </is>
+      </c>
+      <c r="K285" s="3" t="n"/>
+      <c r="L285" s="3" t="n"/>
+      <c r="M285" s="3" t="inlineStr"/>
+      <c r="N285" s="3" t="inlineStr"/>
+      <c r="O285" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P285" s="3" t="inlineStr"/>
+      <c r="Q285" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R285" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="60" customHeight="1">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>EX-0285</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr"/>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>Let's take the discussion offline with the smaller group.</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>この議論は少人数で別途行いましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I286" s="3" t="inlineStr">
+        <is>
+          <t>This is getting detailed — let's take the discussion offline with the smaller group.</t>
+        </is>
+      </c>
+      <c r="J286" s="3" t="inlineStr">
+        <is>
+          <t>話が細かくなってきたので、この議論は少人数で別途行いましょう。</t>
+        </is>
+      </c>
+      <c r="K286" s="3" t="n"/>
+      <c r="L286" s="3" t="n"/>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>Let's take this offline.</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr"/>
+      <c r="O286" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P286" s="3" t="inlineStr"/>
+      <c r="Q286" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R286" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="60" customHeight="1">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>EX-0286</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr"/>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>Thanks for taking my call.</t>
+        </is>
+      </c>
+      <c r="H287" s="3" t="inlineStr">
+        <is>
+          <t>お電話に出ていただきありがとうございます、という電話冒頭の一言。</t>
+        </is>
+      </c>
+      <c r="I287" s="3" t="inlineStr">
+        <is>
+          <t>Thanks for taking my call — I know you're busy.</t>
+        </is>
+      </c>
+      <c r="J287" s="3" t="inlineStr">
+        <is>
+          <t>お忙しいところお電話に出ていただきありがとうございます。</t>
+        </is>
+      </c>
+      <c r="K287" s="3" t="n"/>
+      <c r="L287" s="3" t="n"/>
+      <c r="M287" s="3" t="inlineStr"/>
+      <c r="N287" s="3" t="inlineStr"/>
+      <c r="O287" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P287" s="3" t="inlineStr"/>
+      <c r="Q287" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R287" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="60" customHeight="1">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>EX-0287</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr"/>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>I'll keep this call short.</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>この電話は手短に済ませます、という意味。</t>
+        </is>
+      </c>
+      <c r="I288" s="3" t="inlineStr">
+        <is>
+          <t>I'll keep this call short since I know you have another meeting.</t>
+        </is>
+      </c>
+      <c r="J288" s="3" t="inlineStr">
+        <is>
+          <t>別のミーティングがあると思うので、この電話は手短に済ませます。</t>
+        </is>
+      </c>
+      <c r="K288" s="3" t="n"/>
+      <c r="L288" s="3" t="n"/>
+      <c r="M288" s="3" t="inlineStr"/>
+      <c r="N288" s="3" t="inlineStr"/>
+      <c r="O288" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P288" s="3" t="inlineStr"/>
+      <c r="Q288" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R288" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="60" customHeight="1">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>EX-0288</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr"/>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>Can you give me one moment?</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>少々お待ちいただけますか、という意味。</t>
+        </is>
+      </c>
+      <c r="I289" s="3" t="inlineStr">
+        <is>
+          <t>Can you give me one moment? I need to pull up the file.</t>
+        </is>
+      </c>
+      <c r="J289" s="3" t="inlineStr">
+        <is>
+          <t>少々お待ちいただけますか。ファイルを開く必要があるので。</t>
+        </is>
+      </c>
+      <c r="K289" s="3" t="n"/>
+      <c r="L289" s="3" t="n"/>
+      <c r="M289" s="3" t="inlineStr"/>
+      <c r="N289" s="3" t="inlineStr"/>
+      <c r="O289" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P289" s="3" t="inlineStr"/>
+      <c r="Q289" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R289" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="60" customHeight="1">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>EX-0289</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr"/>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>Sorry, could you speak up a bit?</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>すみません、もう少し大きな声でお願いできますか、という意味。</t>
+        </is>
+      </c>
+      <c r="I290" s="3" t="inlineStr">
+        <is>
+          <t>Sorry, could you speak up a bit? It's a bit noisy on my end.</t>
+        </is>
+      </c>
+      <c r="J290" s="3" t="inlineStr">
+        <is>
+          <t>すみません、もう少し大きな声でお願いできますか。こちらが少し騒がしくて。</t>
+        </is>
+      </c>
+      <c r="K290" s="3" t="n"/>
+      <c r="L290" s="3" t="n"/>
+      <c r="M290" s="3" t="inlineStr"/>
+      <c r="N290" s="3" t="inlineStr"/>
+      <c r="O290" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P290" s="3" t="inlineStr"/>
+      <c r="Q290" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R290" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="60" customHeight="1">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>EX-0290</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr"/>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>I'm calling regarding...</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>~の件でお電話しております、という電話の要件を切り出す定型句。</t>
+        </is>
+      </c>
+      <c r="I291" s="3" t="inlineStr">
+        <is>
+          <t>I'm calling regarding the invoice we sent last week.</t>
+        </is>
+      </c>
+      <c r="J291" s="3" t="inlineStr">
+        <is>
+          <t>先週お送りした請求書の件でお電話しております。</t>
+        </is>
+      </c>
+      <c r="K291" s="3" t="n"/>
+      <c r="L291" s="3" t="n"/>
+      <c r="M291" s="3" t="inlineStr"/>
+      <c r="N291" s="3" t="inlineStr"/>
+      <c r="O291" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P291" s="3" t="inlineStr"/>
+      <c r="Q291" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R291" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="60" customHeight="1">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>EX-0291</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr"/>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>Let me just pull up your file.</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>お客様のファイルを開きますね、という意味。</t>
+        </is>
+      </c>
+      <c r="I292" s="3" t="inlineStr">
+        <is>
+          <t>Let me just pull up your file — one second.</t>
+        </is>
+      </c>
+      <c r="J292" s="3" t="inlineStr">
+        <is>
+          <t>お客様のファイルを開きますね。少々お待ちください。</t>
+        </is>
+      </c>
+      <c r="K292" s="3" t="n"/>
+      <c r="L292" s="3" t="n"/>
+      <c r="M292" s="3" t="inlineStr"/>
+      <c r="N292" s="3" t="inlineStr"/>
+      <c r="O292" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P292" s="3" t="inlineStr"/>
+      <c r="Q292" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R292" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="60" customHeight="1">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>EX-0292</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>I'll send a follow-up email after this call.</t>
+        </is>
+      </c>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>この後フォローアップメールをお送りします、という意味。</t>
+        </is>
+      </c>
+      <c r="I293" s="3" t="inlineStr">
+        <is>
+          <t>I'll send a follow-up email after this call summarizing what we discussed.</t>
+        </is>
+      </c>
+      <c r="J293" s="3" t="inlineStr">
+        <is>
+          <t>この後、話した内容をまとめたフォローアップメールをお送りします。</t>
+        </is>
+      </c>
+      <c r="K293" s="3" t="n"/>
+      <c r="L293" s="3" t="n"/>
+      <c r="M293" s="3" t="inlineStr"/>
+      <c r="N293" s="3" t="inlineStr"/>
+      <c r="O293" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P293" s="3" t="inlineStr"/>
+      <c r="Q293" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R293" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="60" customHeight="1">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>EX-0293</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>Is this a good time, or should I call back later?</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="inlineStr">
+        <is>
+          <t>今お時間よろしいですか、それとも後でかけ直しましょうか、という配慮の表現。</t>
+        </is>
+      </c>
+      <c r="I294" s="3" t="inlineStr">
+        <is>
+          <t>Is this a good time, or should I call back later this afternoon?</t>
+        </is>
+      </c>
+      <c r="J294" s="3" t="inlineStr">
+        <is>
+          <t>今お時間よろしいですか、それとも午後遅くにかけ直しましょうか。</t>
+        </is>
+      </c>
+      <c r="K294" s="3" t="n"/>
+      <c r="L294" s="3" t="n"/>
+      <c r="M294" s="3" t="inlineStr"/>
+      <c r="N294" s="3" t="inlineStr"/>
+      <c r="O294" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P294" s="3" t="inlineStr"/>
+      <c r="Q294" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R294" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="60" customHeight="1">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>EX-0294</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr"/>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>The line's a bit choppy on my end.</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>こちらでは電波が少し悪いようです、という意味。</t>
+        </is>
+      </c>
+      <c r="I295" s="3" t="inlineStr">
+        <is>
+          <t>The line's a bit choppy on my end — can you hear me okay?</t>
+        </is>
+      </c>
+      <c r="J295" s="3" t="inlineStr">
+        <is>
+          <t>こちらでは電波が少し悪いようです。聞こえていますか。</t>
+        </is>
+      </c>
+      <c r="K295" s="3" t="n"/>
+      <c r="L295" s="3" t="n"/>
+      <c r="M295" s="3" t="inlineStr"/>
+      <c r="N295" s="3" t="inlineStr"/>
+      <c r="O295" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P295" s="3" t="inlineStr"/>
+      <c r="Q295" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R295" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="60" customHeight="1">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>EX-0295</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>Let me confirm I have the right number.</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="inlineStr">
+        <is>
+          <t>番号が合っているか確認させてください、という意味。</t>
+        </is>
+      </c>
+      <c r="I296" s="3" t="inlineStr">
+        <is>
+          <t>Let me confirm I have the right number for the billing department.</t>
+        </is>
+      </c>
+      <c r="J296" s="3" t="inlineStr">
+        <is>
+          <t>経理部門の番号が合っているか確認させてください。</t>
+        </is>
+      </c>
+      <c r="K296" s="3" t="n"/>
+      <c r="L296" s="3" t="n"/>
+      <c r="M296" s="3" t="inlineStr"/>
+      <c r="N296" s="3" t="inlineStr"/>
+      <c r="O296" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P296" s="3" t="inlineStr"/>
+      <c r="Q296" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R296" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="60" customHeight="1">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>EX-0296</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr"/>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>I'll patch you through to accounting.</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="inlineStr">
+        <is>
+          <t>経理部門におつなぎします、という意味。</t>
+        </is>
+      </c>
+      <c r="I297" s="3" t="inlineStr">
+        <is>
+          <t>I'll patch you through to accounting — please hold for a moment.</t>
+        </is>
+      </c>
+      <c r="J297" s="3" t="inlineStr">
+        <is>
+          <t>経理部門におつなぎします。少々お待ちください。</t>
+        </is>
+      </c>
+      <c r="K297" s="3" t="n"/>
+      <c r="L297" s="3" t="n"/>
+      <c r="M297" s="3" t="inlineStr">
+        <is>
+          <t>Let me put you through to the manager.</t>
+        </is>
+      </c>
+      <c r="N297" s="3" t="inlineStr"/>
+      <c r="O297" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P297" s="3" t="inlineStr"/>
+      <c r="Q297" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R297" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="60" customHeight="1">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>EX-0297</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr"/>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>Could you hold for just a second?</t>
+        </is>
+      </c>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>少しだけお待ちいただけますか、という意味。</t>
+        </is>
+      </c>
+      <c r="I298" s="3" t="inlineStr">
+        <is>
+          <t>Could you hold for just a second? I'll be right back.</t>
+        </is>
+      </c>
+      <c r="J298" s="3" t="inlineStr">
+        <is>
+          <t>少しだけお待ちいただけますか。すぐに戻ります。</t>
+        </is>
+      </c>
+      <c r="K298" s="3" t="n"/>
+      <c r="L298" s="3" t="n"/>
+      <c r="M298" s="3" t="inlineStr"/>
+      <c r="N298" s="3" t="inlineStr"/>
+      <c r="O298" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P298" s="3" t="inlineStr"/>
+      <c r="Q298" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R298" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="60" customHeight="1">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>EX-0298</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F299" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>Thanks for your time on the phone today.</t>
+        </is>
+      </c>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>本日はお電話でのお時間ありがとうございました、という締めの表現。</t>
+        </is>
+      </c>
+      <c r="I299" s="3" t="inlineStr">
+        <is>
+          <t>Thanks for your time on the phone today — talk soon.</t>
+        </is>
+      </c>
+      <c r="J299" s="3" t="inlineStr">
+        <is>
+          <t>本日はお電話でのお時間ありがとうございました。また近いうちに。</t>
+        </is>
+      </c>
+      <c r="K299" s="3" t="n"/>
+      <c r="L299" s="3" t="n"/>
+      <c r="M299" s="3" t="inlineStr"/>
+      <c r="N299" s="3" t="inlineStr"/>
+      <c r="O299" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P299" s="3" t="inlineStr"/>
+      <c r="Q299" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R299" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="60" customHeight="1">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>EX-0299</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F300" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>I appreciate you calling back so quickly.</t>
+        </is>
+      </c>
+      <c r="H300" s="3" t="inlineStr">
+        <is>
+          <t>すぐに折り返していただきありがとうございます、という意味。</t>
+        </is>
+      </c>
+      <c r="I300" s="3" t="inlineStr">
+        <is>
+          <t>I appreciate you calling back so quickly — I know it's been a busy week.</t>
+        </is>
+      </c>
+      <c r="J300" s="3" t="inlineStr">
+        <is>
+          <t>すぐに折り返していただきありがとうございます。お忙しい週だったと思います。</t>
+        </is>
+      </c>
+      <c r="K300" s="3" t="n"/>
+      <c r="L300" s="3" t="n"/>
+      <c r="M300" s="3" t="inlineStr"/>
+      <c r="N300" s="3" t="inlineStr"/>
+      <c r="O300" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P300" s="3" t="inlineStr"/>
+      <c r="Q300" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R300" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="60" customHeight="1">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>EX-0300</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>Let me read that back to confirm.</t>
+        </is>
+      </c>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>確認のため復唱させてください、という意味。</t>
+        </is>
+      </c>
+      <c r="I301" s="3" t="inlineStr">
+        <is>
+          <t>Let me read that back to confirm — that's 100 units by next Friday, correct?</t>
+        </is>
+      </c>
+      <c r="J301" s="3" t="inlineStr">
+        <is>
+          <t>確認のため復唱させてください。来週金曜までに100個、で合っていますか。</t>
+        </is>
+      </c>
+      <c r="K301" s="3" t="n"/>
+      <c r="L301" s="3" t="n"/>
+      <c r="M301" s="3" t="inlineStr"/>
+      <c r="N301" s="3" t="inlineStr">
+        <is>
+          <t>口頭でのやり取りを確実にするために非常によく使う。</t>
+        </is>
+      </c>
+      <c r="O301" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P301" s="3" t="inlineStr"/>
+      <c r="Q301" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R301" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="60" customHeight="1">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>EX-0301</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>Sorry, we got disconnected there for a second.</t>
+        </is>
+      </c>
+      <c r="H302" s="3" t="inlineStr">
+        <is>
+          <t>すみません、一瞬回線が切れました、という意味。</t>
+        </is>
+      </c>
+      <c r="I302" s="3" t="inlineStr">
+        <is>
+          <t>Sorry, we got disconnected there for a second — could you repeat the last part?</t>
+        </is>
+      </c>
+      <c r="J302" s="3" t="inlineStr">
+        <is>
+          <t>すみません、一瞬回線が切れました。最後の部分をもう一度お願いできますか。</t>
+        </is>
+      </c>
+      <c r="K302" s="3" t="n"/>
+      <c r="L302" s="3" t="n"/>
+      <c r="M302" s="3" t="inlineStr"/>
+      <c r="N302" s="3" t="inlineStr"/>
+      <c r="O302" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P302" s="3" t="inlineStr"/>
+      <c r="Q302" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R302" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="60" customHeight="1">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>EX-0302</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr"/>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>I'll leave my direct line in case you need anything.</t>
+        </is>
+      </c>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>何かあれば直通番号を残しておきます、という意味。</t>
+        </is>
+      </c>
+      <c r="I303" s="3" t="inlineStr">
+        <is>
+          <t>I'll leave my direct line in case you need anything else.</t>
+        </is>
+      </c>
+      <c r="J303" s="3" t="inlineStr">
+        <is>
+          <t>他に何かあれば直通番号を残しておきますね。</t>
+        </is>
+      </c>
+      <c r="K303" s="3" t="n"/>
+      <c r="L303" s="3" t="n"/>
+      <c r="M303" s="3" t="inlineStr"/>
+      <c r="N303" s="3" t="inlineStr"/>
+      <c r="O303" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P303" s="3" t="inlineStr"/>
+      <c r="Q303" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R303" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="60" customHeight="1">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>EX-0303</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>Could you dial into the conference line?</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="inlineStr">
+        <is>
+          <t>電話会議にダイヤルインしていただけますか、という依頼表現。</t>
+        </is>
+      </c>
+      <c r="I304" s="3" t="inlineStr">
+        <is>
+          <t>Could you dial into the conference line at 3 PM sharp?</t>
+        </is>
+      </c>
+      <c r="J304" s="3" t="inlineStr">
+        <is>
+          <t>午後3時ちょうどに電話会議にダイヤルインしていただけますか。</t>
+        </is>
+      </c>
+      <c r="K304" s="3" t="n"/>
+      <c r="L304" s="3" t="n"/>
+      <c r="M304" s="3" t="inlineStr"/>
+      <c r="N304" s="3" t="inlineStr"/>
+      <c r="O304" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P304" s="3" t="inlineStr"/>
+      <c r="Q304" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R304" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="60" customHeight="1">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>EX-0304</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>Let's set up a follow-up call for next week.</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>来週フォローアップの電話を設定しましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I305" s="3" t="inlineStr">
+        <is>
+          <t>Let's set up a follow-up call for next week to check progress.</t>
+        </is>
+      </c>
+      <c r="J305" s="3" t="inlineStr">
+        <is>
+          <t>進捗確認のため、来週フォローアップの電話を設定しましょう。</t>
+        </is>
+      </c>
+      <c r="K305" s="3" t="n"/>
+      <c r="L305" s="3" t="n"/>
+      <c r="M305" s="3" t="inlineStr"/>
+      <c r="N305" s="3" t="inlineStr"/>
+      <c r="O305" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P305" s="3" t="inlineStr"/>
+      <c r="Q305" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R305" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="60" customHeight="1">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>EX-0305</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr"/>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>I don't want to take up too much of your time.</t>
+        </is>
+      </c>
+      <c r="H306" s="3" t="inlineStr">
+        <is>
+          <t>あまりお時間を取らせたくありません、という配慮の表現。</t>
+        </is>
+      </c>
+      <c r="I306" s="3" t="inlineStr">
+        <is>
+          <t>I don't want to take up too much of your time, so I'll keep it brief.</t>
+        </is>
+      </c>
+      <c r="J306" s="3" t="inlineStr">
+        <is>
+          <t>あまりお時間を取らせたくないので、手短にお伝えします。</t>
+        </is>
+      </c>
+      <c r="K306" s="3" t="n"/>
+      <c r="L306" s="3" t="n"/>
+      <c r="M306" s="3" t="inlineStr"/>
+      <c r="N306" s="3" t="inlineStr"/>
+      <c r="O306" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P306" s="3" t="inlineStr"/>
+      <c r="Q306" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R306" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="60" customHeight="1">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>EX-0306</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F307" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>We need this to be a win-win for both sides.</t>
+        </is>
+      </c>
+      <c r="H307" s="3" t="inlineStr">
+        <is>
+          <t>双方にとってwin-winである必要があります、という意味。</t>
+        </is>
+      </c>
+      <c r="I307" s="3" t="inlineStr">
+        <is>
+          <t>We need this to be a win-win for both sides, not just favorable to one party.</t>
+        </is>
+      </c>
+      <c r="J307" s="3" t="inlineStr">
+        <is>
+          <t>一方だけに有利ではなく、双方にとってwin-winである必要があります。</t>
+        </is>
+      </c>
+      <c r="K307" s="3" t="n"/>
+      <c r="L307" s="3" t="n"/>
+      <c r="M307" s="3" t="inlineStr"/>
+      <c r="N307" s="3" t="inlineStr"/>
+      <c r="O307" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P307" s="3" t="inlineStr"/>
+      <c r="Q307" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R307" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="60" customHeight="1">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>EX-0307</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>Let's not nickel-and-dime each other over small details.</t>
+        </is>
+      </c>
+      <c r="H308" s="3" t="inlineStr">
+        <is>
+          <t>細かいことでお互い揉めないようにしましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I308" s="3" t="inlineStr">
+        <is>
+          <t>Let's not nickel-and-dime each other over small details — let's focus on the big picture.</t>
+        </is>
+      </c>
+      <c r="J308" s="3" t="inlineStr">
+        <is>
+          <t>細かいことでお互い揉めず、全体像に集中しましょう。</t>
+        </is>
+      </c>
+      <c r="K308" s="3" t="n"/>
+      <c r="L308" s="3" t="n"/>
+      <c r="M308" s="3" t="inlineStr"/>
+      <c r="N308" s="3" t="inlineStr">
+        <is>
+          <t>「nickel-and-dime」は「細かいことでケチる・揉める」という口語表現。</t>
+        </is>
+      </c>
+      <c r="O308" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P308" s="3" t="inlineStr"/>
+      <c r="Q308" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R308" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="60" customHeight="1">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>EX-0308</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F309" s="3" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>I hear your concerns, but here's our position.</t>
+        </is>
+      </c>
+      <c r="H309" s="3" t="inlineStr">
+        <is>
+          <t>ご懸念は理解しますが、こちらの立場をお伝えします、という意味。</t>
+        </is>
+      </c>
+      <c r="I309" s="3" t="inlineStr">
+        <is>
+          <t>I hear your concerns, but here's our position on the delivery timeline.</t>
+        </is>
+      </c>
+      <c r="J309" s="3" t="inlineStr">
+        <is>
+          <t>ご懸念は理解しますが、納期についてのこちらの立場をお伝えします。</t>
+        </is>
+      </c>
+      <c r="K309" s="3" t="n"/>
+      <c r="L309" s="3" t="n"/>
+      <c r="M309" s="3" t="inlineStr"/>
+      <c r="N309" s="3" t="inlineStr"/>
+      <c r="O309" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P309" s="3" t="inlineStr"/>
+      <c r="Q309" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R309" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="60" customHeight="1">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>EX-0309</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr"/>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>We're willing to compromise, but only to a point.</t>
+        </is>
+      </c>
+      <c r="H310" s="3" t="inlineStr">
+        <is>
+          <t>ある程度までは妥協しますが、限度があります、という意味。</t>
+        </is>
+      </c>
+      <c r="I310" s="3" t="inlineStr">
+        <is>
+          <t>We're willing to compromise, but only to a point — the deadline can't move.</t>
+        </is>
+      </c>
+      <c r="J310" s="3" t="inlineStr">
+        <is>
+          <t>ある程度までは妥協しますが、限度があります。納期は動かせません。</t>
+        </is>
+      </c>
+      <c r="K310" s="3" t="n"/>
+      <c r="L310" s="3" t="n"/>
+      <c r="M310" s="3" t="inlineStr"/>
+      <c r="N310" s="3" t="inlineStr"/>
+      <c r="O310" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P310" s="3" t="inlineStr"/>
+      <c r="Q310" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R310" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="60" customHeight="1">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>EX-0310</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F311" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G311" s="3" t="inlineStr">
+        <is>
+          <t>Let's put pen to paper on this.</t>
+        </is>
+      </c>
+      <c r="H311" s="3" t="inlineStr">
+        <is>
+          <t>これを正式に書面にしましょう、という意味。口頭合意を正式化する提案。</t>
+        </is>
+      </c>
+      <c r="I311" s="3" t="inlineStr">
+        <is>
+          <t>Now that we agree, let's put pen to paper on this.</t>
+        </is>
+      </c>
+      <c r="J311" s="3" t="inlineStr">
+        <is>
+          <t>合意できたので、これを正式に書面にしましょう。</t>
+        </is>
+      </c>
+      <c r="K311" s="3" t="n"/>
+      <c r="L311" s="3" t="n"/>
+      <c r="M311" s="3" t="inlineStr"/>
+      <c r="N311" s="3" t="inlineStr"/>
+      <c r="O311" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P311" s="3" t="inlineStr"/>
+      <c r="Q311" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R311" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="60" customHeight="1">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>EX-0311</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>I'd like to understand your constraints better.</t>
+        </is>
+      </c>
+      <c r="H312" s="3" t="inlineStr">
+        <is>
+          <t>御社の制約についてもっと理解したいです、という意味。</t>
+        </is>
+      </c>
+      <c r="I312" s="3" t="inlineStr">
+        <is>
+          <t>I'd like to understand your constraints better before proposing new terms.</t>
+        </is>
+      </c>
+      <c r="J312" s="3" t="inlineStr">
+        <is>
+          <t>新しい条件を提案する前に、御社の制約についてもっと理解したいです。</t>
+        </is>
+      </c>
+      <c r="K312" s="3" t="n"/>
+      <c r="L312" s="3" t="n"/>
+      <c r="M312" s="3" t="inlineStr"/>
+      <c r="N312" s="3" t="inlineStr"/>
+      <c r="O312" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P312" s="3" t="inlineStr"/>
+      <c r="Q312" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R312" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="60" customHeight="1">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>EX-0312</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F313" s="3" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>That's a non-starter for us.</t>
+        </is>
+      </c>
+      <c r="H313" s="3" t="inlineStr">
+        <is>
+          <t>それは私たちにとって論外です、という強い拒否の表現。</t>
+        </is>
+      </c>
+      <c r="I313" s="3" t="inlineStr">
+        <is>
+          <t>A six-month exclusivity clause is a non-starter for us.</t>
+        </is>
+      </c>
+      <c r="J313" s="3" t="inlineStr">
+        <is>
+          <t>6ヶ月の独占条項は私たちにとって論外です。</t>
+        </is>
+      </c>
+      <c r="K313" s="3" t="n"/>
+      <c r="L313" s="3" t="n"/>
+      <c r="M313" s="3" t="inlineStr"/>
+      <c r="N313" s="3" t="inlineStr">
+        <is>
+          <t>かなり強い拒絶表現。使う場面には注意が必要。</t>
+        </is>
+      </c>
+      <c r="O313" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P313" s="3" t="inlineStr"/>
+      <c r="Q313" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R313" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="60" customHeight="1">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>EX-0313</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>Let's revisit this once we have more data.</t>
+        </is>
+      </c>
+      <c r="H314" s="3" t="inlineStr">
+        <is>
+          <t>もっとデータが揃ってから再検討しましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I314" s="3" t="inlineStr">
+        <is>
+          <t>Let's revisit this once we have more data from the pilot.</t>
+        </is>
+      </c>
+      <c r="J314" s="3" t="inlineStr">
+        <is>
+          <t>パイロットからもっとデータが揃ってから再検討しましょう。</t>
+        </is>
+      </c>
+      <c r="K314" s="3" t="n"/>
+      <c r="L314" s="3" t="n"/>
+      <c r="M314" s="3" t="inlineStr"/>
+      <c r="N314" s="3" t="inlineStr"/>
+      <c r="O314" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P314" s="3" t="inlineStr"/>
+      <c r="Q314" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R314" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="60" customHeight="1">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>EX-0314</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>We appreciate your flexibility on this.</t>
+        </is>
+      </c>
+      <c r="H315" s="3" t="inlineStr">
+        <is>
+          <t>この点での柔軟な対応に感謝します、という意味。</t>
+        </is>
+      </c>
+      <c r="I315" s="3" t="inlineStr">
+        <is>
+          <t>We appreciate your flexibility on this — it really helps us out.</t>
+        </is>
+      </c>
+      <c r="J315" s="3" t="inlineStr">
+        <is>
+          <t>この点での柔軟な対応に感謝します。本当に助かります。</t>
+        </is>
+      </c>
+      <c r="K315" s="3" t="n"/>
+      <c r="L315" s="3" t="n"/>
+      <c r="M315" s="3" t="inlineStr"/>
+      <c r="N315" s="3" t="inlineStr"/>
+      <c r="O315" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P315" s="3" t="inlineStr"/>
+      <c r="Q315" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R315" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="60" customHeight="1">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>EX-0315</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>Let's not let this stall the whole deal.</t>
+        </is>
+      </c>
+      <c r="H316" s="3" t="inlineStr">
+        <is>
+          <t>これで取引全体が停滞しないようにしましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I316" s="3" t="inlineStr">
+        <is>
+          <t>It's a small gap — let's not let this stall the whole deal.</t>
+        </is>
+      </c>
+      <c r="J316" s="3" t="inlineStr">
+        <is>
+          <t>わずかな差なので、これで取引全体が停滞しないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="K316" s="3" t="n"/>
+      <c r="L316" s="3" t="n"/>
+      <c r="M316" s="3" t="inlineStr"/>
+      <c r="N316" s="3" t="inlineStr"/>
+      <c r="O316" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P316" s="3" t="inlineStr"/>
+      <c r="Q316" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R316" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="60" customHeight="1">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>EX-0316</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F317" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G317" s="3" t="inlineStr">
+        <is>
+          <t>I completely understand if you can't.</t>
+        </is>
+      </c>
+      <c r="H317" s="3" t="inlineStr">
+        <is>
+          <t>できなくても全く問題ありません、という依頼相手への配慮表現。</t>
+        </is>
+      </c>
+      <c r="I317" s="3" t="inlineStr">
+        <is>
+          <t>I completely understand if you can't make it work on such short notice.</t>
+        </is>
+      </c>
+      <c r="J317" s="3" t="inlineStr">
+        <is>
+          <t>急な話なので、できなくても全く問題ありません。</t>
+        </is>
+      </c>
+      <c r="K317" s="3" t="n"/>
+      <c r="L317" s="3" t="n"/>
+      <c r="M317" s="3" t="inlineStr"/>
+      <c r="N317" s="3" t="inlineStr"/>
+      <c r="O317" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P317" s="3" t="inlineStr"/>
+      <c r="Q317" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R317" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="60" customHeight="1">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>EX-0317</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G318" s="3" t="inlineStr">
+        <is>
+          <t>Would you be opposed to...?</t>
+        </is>
+      </c>
+      <c r="H318" s="3" t="inlineStr">
+        <is>
+          <t>~に反対ではありませんか、という控えめな依頼・提案の表現。</t>
+        </is>
+      </c>
+      <c r="I318" s="3" t="inlineStr">
+        <is>
+          <t>Would you be opposed to pushing the deadline by two days?</t>
+        </is>
+      </c>
+      <c r="J318" s="3" t="inlineStr">
+        <is>
+          <t>締切を2日延ばすことに反対ではありませんか。</t>
+        </is>
+      </c>
+      <c r="K318" s="3" t="n"/>
+      <c r="L318" s="3" t="n"/>
+      <c r="M318" s="3" t="inlineStr"/>
+      <c r="N318" s="3" t="inlineStr"/>
+      <c r="O318" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P318" s="3" t="inlineStr"/>
+      <c r="Q318" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R318" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="60" customHeight="1">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>EX-0318</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>謝罪,依頼</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F319" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G319" s="3" t="inlineStr">
+        <is>
+          <t>I'm sorry to keep pushing on this, but...</t>
+        </is>
+      </c>
+      <c r="H319" s="3" t="inlineStr">
+        <is>
+          <t>しつこいようで申し訳ないのですが、という意味。何度目かのお願いをする際の前置き。</t>
+        </is>
+      </c>
+      <c r="I319" s="3" t="inlineStr">
+        <is>
+          <t>I'm sorry to keep pushing on this, but could you confirm by tomorrow?</t>
+        </is>
+      </c>
+      <c r="J319" s="3" t="inlineStr">
+        <is>
+          <t>しつこいようで申し訳ないのですが、明日までにご確認いただけますか。</t>
+        </is>
+      </c>
+      <c r="K319" s="3" t="n"/>
+      <c r="L319" s="3" t="n"/>
+      <c r="M319" s="3" t="inlineStr"/>
+      <c r="N319" s="3" t="inlineStr"/>
+      <c r="O319" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P319" s="3" t="inlineStr"/>
+      <c r="Q319" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R319" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="60" customHeight="1">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>EX-0319</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F320" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G320" s="3" t="inlineStr">
+        <is>
+          <t>That's more than I can take on right now.</t>
+        </is>
+      </c>
+      <c r="H320" s="3" t="inlineStr">
+        <is>
+          <t>今の私にはそれ以上は引き受けられません、という意味。</t>
+        </is>
+      </c>
+      <c r="I320" s="3" t="inlineStr">
+        <is>
+          <t>I'd love to help, but that's more than I can take on right now.</t>
+        </is>
+      </c>
+      <c r="J320" s="3" t="inlineStr">
+        <is>
+          <t>力になりたいのですが、今の私にはそれ以上は引き受けられません。</t>
+        </is>
+      </c>
+      <c r="K320" s="3" t="n"/>
+      <c r="L320" s="3" t="n"/>
+      <c r="M320" s="3" t="inlineStr"/>
+      <c r="N320" s="3" t="inlineStr"/>
+      <c r="O320" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P320" s="3" t="inlineStr"/>
+      <c r="Q320" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R320" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="60" customHeight="1">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>EX-0320</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F321" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G321" s="3" t="inlineStr">
+        <is>
+          <t>I really appreciate you considering it.</t>
+        </is>
+      </c>
+      <c r="H321" s="3" t="inlineStr">
+        <is>
+          <t>ご検討いただけるだけでとても感謝しています、という意味。</t>
+        </is>
+      </c>
+      <c r="I321" s="3" t="inlineStr">
+        <is>
+          <t>I really appreciate you considering it, even if the answer is no.</t>
+        </is>
+      </c>
+      <c r="J321" s="3" t="inlineStr">
+        <is>
+          <t>結果がノーであっても、ご検討いただけるだけでとても感謝しています。</t>
+        </is>
+      </c>
+      <c r="K321" s="3" t="n"/>
+      <c r="L321" s="3" t="n"/>
+      <c r="M321" s="3" t="inlineStr"/>
+      <c r="N321" s="3" t="inlineStr"/>
+      <c r="O321" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P321" s="3" t="inlineStr"/>
+      <c r="Q321" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R321" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="60" customHeight="1">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>EX-0321</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F322" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G322" s="3" t="inlineStr">
+        <is>
+          <t>Let me check my schedule and get back to you.</t>
+        </is>
+      </c>
+      <c r="H322" s="3" t="inlineStr">
+        <is>
+          <t>スケジュールを確認して折り返します、という保留の表現。</t>
+        </is>
+      </c>
+      <c r="I322" s="3" t="inlineStr">
+        <is>
+          <t>Let me check my schedule and get back to you by tomorrow.</t>
+        </is>
+      </c>
+      <c r="J322" s="3" t="inlineStr">
+        <is>
+          <t>スケジュールを確認して、明日までに折り返します。</t>
+        </is>
+      </c>
+      <c r="K322" s="3" t="n"/>
+      <c r="L322" s="3" t="n"/>
+      <c r="M322" s="3" t="inlineStr">
+        <is>
+          <t>Let me get back to you on that.</t>
+        </is>
+      </c>
+      <c r="N322" s="3" t="inlineStr"/>
+      <c r="O322" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P322" s="3" t="inlineStr"/>
+      <c r="Q322" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R322" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="60" customHeight="1">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>EX-0322</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>謝罪,依頼</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F323" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G323" s="3" t="inlineStr">
+        <is>
+          <t>I hate to be a bother, but...</t>
+        </is>
+      </c>
+      <c r="H323" s="3" t="inlineStr">
+        <is>
+          <t>お手数をおかけして恐縮ですが、という依頼の前置き。</t>
+        </is>
+      </c>
+      <c r="I323" s="3" t="inlineStr">
+        <is>
+          <t>I hate to be a bother, but could you resend that file?</t>
+        </is>
+      </c>
+      <c r="J323" s="3" t="inlineStr">
+        <is>
+          <t>お手数をおかけして恐縮ですが、そのファイルを再送していただけますか。</t>
+        </is>
+      </c>
+      <c r="K323" s="3" t="n"/>
+      <c r="L323" s="3" t="n"/>
+      <c r="M323" s="3" t="inlineStr"/>
+      <c r="N323" s="3" t="inlineStr"/>
+      <c r="O323" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P323" s="3" t="inlineStr"/>
+      <c r="Q323" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R323" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="60" customHeight="1">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>EX-0323</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F324" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G324" s="3" t="inlineStr">
+        <is>
+          <t>I'm swamped this week, so it might have to wait.</t>
+        </is>
+      </c>
+      <c r="H324" s="3" t="inlineStr">
+        <is>
+          <t>今週は手一杯なので、少し待っていただくかもしれません、という意味。</t>
+        </is>
+      </c>
+      <c r="I324" s="3" t="inlineStr">
+        <is>
+          <t>I'm swamped this week, so it might have to wait until Monday.</t>
+        </is>
+      </c>
+      <c r="J324" s="3" t="inlineStr">
+        <is>
+          <t>今週は手一杯なので、月曜まで待っていただくかもしれません。</t>
+        </is>
+      </c>
+      <c r="K324" s="3" t="n"/>
+      <c r="L324" s="3" t="n"/>
+      <c r="M324" s="3" t="inlineStr"/>
+      <c r="N324" s="3" t="inlineStr"/>
+      <c r="O324" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P324" s="3" t="inlineStr"/>
+      <c r="Q324" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R324" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="60" customHeight="1">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>EX-0324</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F325" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G325" s="3" t="inlineStr">
+        <is>
+          <t>I wish I could help, but my hands are tied.</t>
+        </is>
+      </c>
+      <c r="H325" s="3" t="inlineStr">
+        <is>
+          <t>力になりたいのですが、身動きが取れません、という意味。</t>
+        </is>
+      </c>
+      <c r="I325" s="3" t="inlineStr">
+        <is>
+          <t>I wish I could help, but my hands are tied on pricing decisions.</t>
+        </is>
+      </c>
+      <c r="J325" s="3" t="inlineStr">
+        <is>
+          <t>力になりたいのですが、価格決定については身動きが取れません。</t>
+        </is>
+      </c>
+      <c r="K325" s="3" t="n"/>
+      <c r="L325" s="3" t="n"/>
+      <c r="M325" s="3" t="inlineStr"/>
+      <c r="N325" s="3" t="inlineStr">
+        <is>
+          <t>「hands are tied」は「権限がなく何もできない」の定番表現。</t>
+        </is>
+      </c>
+      <c r="O325" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P325" s="3" t="inlineStr"/>
+      <c r="Q325" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R325" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="60" customHeight="1">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>EX-0325</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F326" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G326" s="3" t="inlineStr">
+        <is>
+          <t>Consider it done.</t>
+        </is>
+      </c>
+      <c r="H326" s="3" t="inlineStr">
+        <is>
+          <t>承知しました、お任せください、という頼もしい快諾の表現。</t>
+        </is>
+      </c>
+      <c r="I326" s="3" t="inlineStr">
+        <is>
+          <t>Need this by Friday? Consider it done.</t>
+        </is>
+      </c>
+      <c r="J326" s="3" t="inlineStr">
+        <is>
+          <t>金曜までに必要ですか？承知しました、お任せください。</t>
+        </is>
+      </c>
+      <c r="K326" s="3" t="n"/>
+      <c r="L326" s="3" t="n"/>
+      <c r="M326" s="3" t="inlineStr"/>
+      <c r="N326" s="3" t="inlineStr"/>
+      <c r="O326" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P326" s="3" t="inlineStr"/>
+      <c r="Q326" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R326" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="60" customHeight="1">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>EX-0326</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr"/>
+      <c r="E327" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F327" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G327" s="3" t="inlineStr">
+        <is>
+          <t>I hope you had a good break.</t>
+        </is>
+      </c>
+      <c r="H327" s="3" t="inlineStr">
+        <is>
+          <t>良い休暇を過ごされたことと思います、というメール冒頭の一言。</t>
+        </is>
+      </c>
+      <c r="I327" s="3" t="inlineStr">
+        <is>
+          <t>I hope you had a good break — let's pick up where we left off.</t>
+        </is>
+      </c>
+      <c r="J327" s="3" t="inlineStr">
+        <is>
+          <t>良い休暇を過ごされたことと思います。続きを再開しましょう。</t>
+        </is>
+      </c>
+      <c r="K327" s="3" t="n"/>
+      <c r="L327" s="3" t="n"/>
+      <c r="M327" s="3" t="inlineStr"/>
+      <c r="N327" s="3" t="inlineStr"/>
+      <c r="O327" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P327" s="3" t="inlineStr"/>
+      <c r="Q327" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R327" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="60" customHeight="1">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>EX-0327</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F328" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G328" s="3" t="inlineStr">
+        <is>
+          <t>Apologies for the mass email.</t>
+        </is>
+      </c>
+      <c r="H328" s="3" t="inlineStr">
+        <is>
+          <t>一斉送信のメールで失礼します、という意味。</t>
+        </is>
+      </c>
+      <c r="I328" s="3" t="inlineStr">
+        <is>
+          <t>Apologies for the mass email — wanted to make sure everyone got this in time.</t>
+        </is>
+      </c>
+      <c r="J328" s="3" t="inlineStr">
+        <is>
+          <t>一斉送信のメールで失礼します。皆様に確実に届くようにしたく。</t>
+        </is>
+      </c>
+      <c r="K328" s="3" t="n"/>
+      <c r="L328" s="3" t="n"/>
+      <c r="M328" s="3" t="inlineStr"/>
+      <c r="N328" s="3" t="inlineStr"/>
+      <c r="O328" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P328" s="3" t="inlineStr"/>
+      <c r="Q328" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R328" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="60" customHeight="1">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>EX-0328</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr"/>
+      <c r="E329" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F329" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G329" s="3" t="inlineStr">
+        <is>
+          <t>Just to close the loop on this...</t>
+        </is>
+      </c>
+      <c r="H329" s="3" t="inlineStr">
+        <is>
+          <t>この件について締めくくると、という意味。話の結論を伝える前置き。</t>
+        </is>
+      </c>
+      <c r="I329" s="3" t="inlineStr">
+        <is>
+          <t>Just to close the loop on this, we've decided to go with option B.</t>
+        </is>
+      </c>
+      <c r="J329" s="3" t="inlineStr">
+        <is>
+          <t>この件について締めくくると、選択肢Bで進めることになりました。</t>
+        </is>
+      </c>
+      <c r="K329" s="3" t="n"/>
+      <c r="L329" s="3" t="n"/>
+      <c r="M329" s="3" t="inlineStr"/>
+      <c r="N329" s="3" t="inlineStr"/>
+      <c r="O329" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P329" s="3" t="inlineStr"/>
+      <c r="Q329" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R329" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="60" customHeight="1">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>EX-0329</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C330" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F330" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G330" s="3" t="inlineStr">
+        <is>
+          <t>Let me know if I've misunderstood anything.</t>
+        </is>
+      </c>
+      <c r="H330" s="3" t="inlineStr">
+        <is>
+          <t>何か誤解していたら教えてください、という確認の表現。</t>
+        </is>
+      </c>
+      <c r="I330" s="3" t="inlineStr">
+        <is>
+          <t>Let me know if I've misunderstood anything in the requirements.</t>
+        </is>
+      </c>
+      <c r="J330" s="3" t="inlineStr">
+        <is>
+          <t>要件について何か誤解していたら教えてください。</t>
+        </is>
+      </c>
+      <c r="K330" s="3" t="n"/>
+      <c r="L330" s="3" t="n"/>
+      <c r="M330" s="3" t="inlineStr"/>
+      <c r="N330" s="3" t="inlineStr"/>
+      <c r="O330" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P330" s="3" t="inlineStr"/>
+      <c r="Q330" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R330" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="60" customHeight="1">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>EX-0330</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="inlineStr"/>
+      <c r="E331" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F331" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G331" s="3" t="inlineStr">
+        <is>
+          <t>I'll be out of office next week, but John will cover for me.</t>
+        </is>
+      </c>
+      <c r="H331" s="3" t="inlineStr">
+        <is>
+          <t>来週不在ですが、ジョンが対応します、という不在連絡の定型句。</t>
+        </is>
+      </c>
+      <c r="I331" s="3" t="inlineStr">
+        <is>
+          <t>I'll be out of office next week, but John will cover for me on urgent matters.</t>
+        </is>
+      </c>
+      <c r="J331" s="3" t="inlineStr">
+        <is>
+          <t>来週不在ですが、緊急の件はジョンが対応します。</t>
+        </is>
+      </c>
+      <c r="K331" s="3" t="n"/>
+      <c r="L331" s="3" t="n"/>
+      <c r="M331" s="3" t="inlineStr"/>
+      <c r="N331" s="3" t="inlineStr"/>
+      <c r="O331" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P331" s="3" t="inlineStr"/>
+      <c r="Q331" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R331" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="60" customHeight="1">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>EX-0331</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F332" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G332" s="3" t="inlineStr">
+        <is>
+          <t>Thanks again for your understanding.</t>
+        </is>
+      </c>
+      <c r="H332" s="3" t="inlineStr">
+        <is>
+          <t>ご理解いただきありがとうございます、という締めの表現。</t>
+        </is>
+      </c>
+      <c r="I332" s="3" t="inlineStr">
+        <is>
+          <t>Thanks again for your understanding regarding the schedule change.</t>
+        </is>
+      </c>
+      <c r="J332" s="3" t="inlineStr">
+        <is>
+          <t>スケジュール変更についてご理解いただきありがとうございます。</t>
+        </is>
+      </c>
+      <c r="K332" s="3" t="n"/>
+      <c r="L332" s="3" t="n"/>
+      <c r="M332" s="3" t="inlineStr"/>
+      <c r="N332" s="3" t="inlineStr"/>
+      <c r="O332" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P332" s="3" t="inlineStr"/>
+      <c r="Q332" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R332" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="60" customHeight="1">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>EX-0332</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F333" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G333" s="3" t="inlineStr">
+        <is>
+          <t>Apologies again for any inconvenience this may cause.</t>
+        </is>
+      </c>
+      <c r="H333" s="3" t="inlineStr">
+        <is>
+          <t>ご不便をおかけし重ねてお詫び申し上げます、という丁寧な謝罪表現。</t>
+        </is>
+      </c>
+      <c r="I333" s="3" t="inlineStr">
+        <is>
+          <t>Apologies again for any inconvenience this may cause during the transition.</t>
+        </is>
+      </c>
+      <c r="J333" s="3" t="inlineStr">
+        <is>
+          <t>移行期間中にご不便をおかけし重ねてお詫び申し上げます。</t>
+        </is>
+      </c>
+      <c r="K333" s="3" t="n"/>
+      <c r="L333" s="3" t="n"/>
+      <c r="M333" s="3" t="inlineStr"/>
+      <c r="N333" s="3" t="inlineStr"/>
+      <c r="O333" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P333" s="3" t="inlineStr"/>
+      <c r="Q333" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R333" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="60" customHeight="1">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>EX-0333</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr"/>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F334" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G334" s="3" t="inlineStr">
+        <is>
+          <t>I've attached the revised version for your review.</t>
+        </is>
+      </c>
+      <c r="H334" s="3" t="inlineStr">
+        <is>
+          <t>ご確認用に修正版を添付しました、という意味。</t>
+        </is>
+      </c>
+      <c r="I334" s="3" t="inlineStr">
+        <is>
+          <t>I've attached the revised version for your review — let me know your thoughts.</t>
+        </is>
+      </c>
+      <c r="J334" s="3" t="inlineStr">
+        <is>
+          <t>ご確認用に修正版を添付しました。ご感想をお聞かせください。</t>
+        </is>
+      </c>
+      <c r="K334" s="3" t="n"/>
+      <c r="L334" s="3" t="n"/>
+      <c r="M334" s="3" t="inlineStr"/>
+      <c r="N334" s="3" t="inlineStr"/>
+      <c r="O334" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P334" s="3" t="inlineStr"/>
+      <c r="Q334" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R334" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="60" customHeight="1">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>EX-0334</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F335" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G335" s="3" t="inlineStr">
+        <is>
+          <t>Let's touch base once you're back.</t>
+        </is>
+      </c>
+      <c r="H335" s="3" t="inlineStr">
+        <is>
+          <t>戻られたら改めて連絡を取り合いましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I335" s="3" t="inlineStr">
+        <is>
+          <t>Let's touch base once you're back from your trip.</t>
+        </is>
+      </c>
+      <c r="J335" s="3" t="inlineStr">
+        <is>
+          <t>出張から戻られたら改めて連絡を取り合いましょう。</t>
+        </is>
+      </c>
+      <c r="K335" s="3" t="n"/>
+      <c r="L335" s="3" t="n"/>
+      <c r="M335" s="3" t="inlineStr"/>
+      <c r="N335" s="3" t="inlineStr"/>
+      <c r="O335" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P335" s="3" t="inlineStr"/>
+      <c r="Q335" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R335" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="60" customHeight="1">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>EX-0335</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F336" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G336" s="3" t="inlineStr">
+        <is>
+          <t>I wanted to flag this before it becomes urgent.</t>
+        </is>
+      </c>
+      <c r="H336" s="3" t="inlineStr">
+        <is>
+          <t>緊急になる前にお伝えしておきたく、という早めの連絡を示す表現。</t>
+        </is>
+      </c>
+      <c r="I336" s="3" t="inlineStr">
+        <is>
+          <t>I wanted to flag this before it becomes urgent — the server capacity is running low.</t>
+        </is>
+      </c>
+      <c r="J336" s="3" t="inlineStr">
+        <is>
+          <t>緊急になる前にお伝えしておきたいのですが、サーバー容量が少なくなっています。</t>
+        </is>
+      </c>
+      <c r="K336" s="3" t="n"/>
+      <c r="L336" s="3" t="n"/>
+      <c r="M336" s="3" t="inlineStr"/>
+      <c r="N336" s="3" t="inlineStr"/>
+      <c r="O336" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P336" s="3" t="inlineStr"/>
+      <c r="Q336" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R336" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="60" customHeight="1">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>EX-0336</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F337" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G337" s="3" t="inlineStr">
+        <is>
+          <t>You're a lifesaver.</t>
+        </is>
+      </c>
+      <c r="H337" s="3" t="inlineStr">
+        <is>
+          <t>本当に助かりました、という強い感謝の表現。</t>
+        </is>
+      </c>
+      <c r="I337" s="3" t="inlineStr">
+        <is>
+          <t>You finished that report for me? You're a lifesaver.</t>
+        </is>
+      </c>
+      <c r="J337" s="3" t="inlineStr">
+        <is>
+          <t>あの報告書を代わりに仕上げてくれたの？本当に助かりました。</t>
+        </is>
+      </c>
+      <c r="K337" s="3" t="n"/>
+      <c r="L337" s="3" t="n"/>
+      <c r="M337" s="3" t="inlineStr"/>
+      <c r="N337" s="3" t="inlineStr"/>
+      <c r="O337" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P337" s="3" t="inlineStr"/>
+      <c r="Q337" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R337" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="60" customHeight="1">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>EX-0337</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr"/>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F338" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G338" s="3" t="inlineStr">
+        <is>
+          <t>I owe you a coffee for this.</t>
+        </is>
+      </c>
+      <c r="H338" s="3" t="inlineStr">
+        <is>
+          <t>このお礼にコーヒーをおごります、という軽いお礼の表現。</t>
+        </is>
+      </c>
+      <c r="I338" s="3" t="inlineStr">
+        <is>
+          <t>Thanks for covering my shift — I owe you a coffee for this.</t>
+        </is>
+      </c>
+      <c r="J338" s="3" t="inlineStr">
+        <is>
+          <t>シフトを代わってくれてありがとう。このお礼にコーヒーをおごるよ。</t>
+        </is>
+      </c>
+      <c r="K338" s="3" t="n"/>
+      <c r="L338" s="3" t="n"/>
+      <c r="M338" s="3" t="inlineStr"/>
+      <c r="N338" s="3" t="inlineStr"/>
+      <c r="O338" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P338" s="3" t="inlineStr"/>
+      <c r="Q338" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R338" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="60" customHeight="1">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>EX-0338</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>同意・肯定,相槌・共感</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F339" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G339" s="3" t="inlineStr">
+        <is>
+          <t>That makes two of us.</t>
+        </is>
+      </c>
+      <c r="H339" s="3" t="inlineStr">
+        <is>
+          <t>私も同じです、という意味。相手と同じ状況・気持ちであることを示す表現。</t>
+        </is>
+      </c>
+      <c r="I339" s="3" t="inlineStr">
+        <is>
+          <t>I'm exhausted today. — That makes two of us.</t>
+        </is>
+      </c>
+      <c r="J339" s="3" t="inlineStr">
+        <is>
+          <t>今日はもうくたくただよ。—私も同じです。</t>
+        </is>
+      </c>
+      <c r="K339" s="3" t="n"/>
+      <c r="L339" s="3" t="n"/>
+      <c r="M339" s="3" t="inlineStr"/>
+      <c r="N339" s="3" t="inlineStr"/>
+      <c r="O339" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P339" s="3" t="inlineStr"/>
+      <c r="Q339" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R339" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="60" customHeight="1">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>EX-0339</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C340" s="3" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F340" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G340" s="3" t="inlineStr">
+        <is>
+          <t>I hear you.</t>
+        </is>
+      </c>
+      <c r="H340" s="3" t="inlineStr">
+        <is>
+          <t>お気持ちわかります、という共感の相槌表現。</t>
+        </is>
+      </c>
+      <c r="I340" s="3" t="inlineStr">
+        <is>
+          <t>It's been a tough week. — I hear you, it's been rough for everyone.</t>
+        </is>
+      </c>
+      <c r="J340" s="3" t="inlineStr">
+        <is>
+          <t>大変な一週間だったよ。—お気持ちわかります、みんな大変でした。</t>
+        </is>
+      </c>
+      <c r="K340" s="3" t="n"/>
+      <c r="L340" s="3" t="n"/>
+      <c r="M340" s="3" t="inlineStr"/>
+      <c r="N340" s="3" t="inlineStr"/>
+      <c r="O340" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P340" s="3" t="inlineStr"/>
+      <c r="Q340" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R340" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="60" customHeight="1">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>EX-0340</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F341" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G341" s="3" t="inlineStr">
+        <is>
+          <t>Tell me about it.</t>
+        </is>
+      </c>
+      <c r="H341" s="3" t="inlineStr">
+        <is>
+          <t>まさにそれです、よくわかります、という強い共感の相槌表現。</t>
+        </is>
+      </c>
+      <c r="I341" s="3" t="inlineStr">
+        <is>
+          <t>Traffic was awful this morning. — Tell me about it.</t>
+        </is>
+      </c>
+      <c r="J341" s="3" t="inlineStr">
+        <is>
+          <t>今朝の渋滞はひどかったよ。—まさにそれです。</t>
+        </is>
+      </c>
+      <c r="K341" s="3" t="n"/>
+      <c r="L341" s="3" t="n"/>
+      <c r="M341" s="3" t="inlineStr"/>
+      <c r="N341" s="3" t="inlineStr">
+        <is>
+          <t>皮肉ではなく共感を示す口語表現。トーンに注意。</t>
+        </is>
+      </c>
+      <c r="O341" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P341" s="3" t="inlineStr"/>
+      <c r="Q341" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R341" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="60" customHeight="1">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>EX-0341</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr"/>
+      <c r="E342" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F342" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G342" s="3" t="inlineStr">
+        <is>
+          <t>Speak of the devil!</t>
+        </is>
+      </c>
+      <c r="H342" s="3" t="inlineStr">
+        <is>
+          <t>噂をすれば、という意味。話題にしていた人が現れたときの表現。</t>
+        </is>
+      </c>
+      <c r="I342" s="3" t="inlineStr">
+        <is>
+          <t>Speak of the devil! We were just talking about you.</t>
+        </is>
+      </c>
+      <c r="J342" s="3" t="inlineStr">
+        <is>
+          <t>噂をすれば！ちょうどあなたの話をしていたところです。</t>
+        </is>
+      </c>
+      <c r="K342" s="3" t="n"/>
+      <c r="L342" s="3" t="n"/>
+      <c r="M342" s="3" t="inlineStr"/>
+      <c r="N342" s="3" t="inlineStr"/>
+      <c r="O342" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P342" s="3" t="inlineStr"/>
+      <c r="Q342" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R342" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="60" customHeight="1">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>EX-0342</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F343" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G343" s="3" t="inlineStr">
+        <is>
+          <t>That's rough.</t>
+        </is>
+      </c>
+      <c r="H343" s="3" t="inlineStr">
+        <is>
+          <t>それは大変でしたね、という同情・共感を示す表現。</t>
+        </is>
+      </c>
+      <c r="I343" s="3" t="inlineStr">
+        <is>
+          <t>My flight got cancelled twice. — That's rough.</t>
+        </is>
+      </c>
+      <c r="J343" s="3" t="inlineStr">
+        <is>
+          <t>フライトが2回もキャンセルになったんだ。—それは大変でしたね。</t>
+        </is>
+      </c>
+      <c r="K343" s="3" t="n"/>
+      <c r="L343" s="3" t="n"/>
+      <c r="M343" s="3" t="inlineStr"/>
+      <c r="N343" s="3" t="inlineStr"/>
+      <c r="O343" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P343" s="3" t="inlineStr"/>
+      <c r="Q343" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R343" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="60" customHeight="1">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>EX-0343</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr"/>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F344" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G344" s="3" t="inlineStr">
+        <is>
+          <t>Good to see a friendly face.</t>
+        </is>
+      </c>
+      <c r="H344" s="3" t="inlineStr">
+        <is>
+          <t>見知った顔に会えて嬉しいです、という意味。</t>
+        </is>
+      </c>
+      <c r="I344" s="3" t="inlineStr">
+        <is>
+          <t>Good to see a friendly face at this conference.</t>
+        </is>
+      </c>
+      <c r="J344" s="3" t="inlineStr">
+        <is>
+          <t>この会議で見知った顔に会えて嬉しいです。</t>
+        </is>
+      </c>
+      <c r="K344" s="3" t="n"/>
+      <c r="L344" s="3" t="n"/>
+      <c r="M344" s="3" t="inlineStr"/>
+      <c r="N344" s="3" t="inlineStr"/>
+      <c r="O344" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P344" s="3" t="inlineStr"/>
+      <c r="Q344" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R344" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="60" customHeight="1">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>EX-0344</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F345" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G345" s="3" t="inlineStr">
+        <is>
+          <t>Let's catch up properly sometime.</t>
+        </is>
+      </c>
+      <c r="H345" s="3" t="inlineStr">
+        <is>
+          <t>今度ゆっくり近況報告しましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I345" s="3" t="inlineStr">
+        <is>
+          <t>We haven't talked in ages — let's catch up properly sometime.</t>
+        </is>
+      </c>
+      <c r="J345" s="3" t="inlineStr">
+        <is>
+          <t>しばらく話していないので、今度ゆっくり近況報告しましょう。</t>
+        </is>
+      </c>
+      <c r="K345" s="3" t="n"/>
+      <c r="L345" s="3" t="n"/>
+      <c r="M345" s="3" t="inlineStr"/>
+      <c r="N345" s="3" t="inlineStr"/>
+      <c r="O345" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P345" s="3" t="inlineStr"/>
+      <c r="Q345" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R345" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="60" customHeight="1">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>EX-0345</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr"/>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F346" s="3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G346" s="3" t="inlineStr">
+        <is>
+          <t>I'll let you get on with your day.</t>
+        </is>
+      </c>
+      <c r="H346" s="3" t="inlineStr">
+        <is>
+          <t>お邪魔してすみません、この辺で、という会話を切り上げる表現。</t>
+        </is>
+      </c>
+      <c r="I346" s="3" t="inlineStr">
+        <is>
+          <t>I'll let you get on with your day — thanks for chatting.</t>
+        </is>
+      </c>
+      <c r="J346" s="3" t="inlineStr">
+        <is>
+          <t>お邪魔してすみません、この辺で。お話しできてよかったです。</t>
+        </is>
+      </c>
+      <c r="K346" s="3" t="n"/>
+      <c r="L346" s="3" t="n"/>
+      <c r="M346" s="3" t="inlineStr"/>
+      <c r="N346" s="3" t="inlineStr"/>
+      <c r="O346" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P346" s="3" t="inlineStr"/>
+      <c r="Q346" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R346" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="60" customHeight="1">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>EX-0346</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F347" s="3" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G347" s="3" t="inlineStr">
+        <is>
+          <t>I take full responsibility for this mistake.</t>
+        </is>
+      </c>
+      <c r="H347" s="3" t="inlineStr">
+        <is>
+          <t>この件については全面的に私の責任です、という強い謝罪・責任表明の表現。</t>
+        </is>
+      </c>
+      <c r="I347" s="3" t="inlineStr">
+        <is>
+          <t>I take full responsibility for this mistake and will make sure it doesn't happen again.</t>
+        </is>
+      </c>
+      <c r="J347" s="3" t="inlineStr">
+        <is>
+          <t>この件については全面的に私の責任です。二度と起きないようにいたします。</t>
+        </is>
+      </c>
+      <c r="K347" s="3" t="n"/>
+      <c r="L347" s="3" t="n"/>
+      <c r="M347" s="3" t="inlineStr"/>
+      <c r="N347" s="3" t="inlineStr"/>
+      <c r="O347" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P347" s="3" t="inlineStr"/>
+      <c r="Q347" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R347" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="60" customHeight="1">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>EX-0347</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C348" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F348" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G348" s="3" t="inlineStr">
+        <is>
+          <t>That wasn't my intention, and I apologize for the confusion.</t>
+        </is>
+      </c>
+      <c r="H348" s="3" t="inlineStr">
+        <is>
+          <t>そのつもりはなく、混乱させてしまい申し訳ありません、という意味。</t>
+        </is>
+      </c>
+      <c r="I348" s="3" t="inlineStr">
+        <is>
+          <t>That wasn't my intention, and I apologize for the confusion my email caused.</t>
+        </is>
+      </c>
+      <c r="J348" s="3" t="inlineStr">
+        <is>
+          <t>そのつもりはなく、私のメールで混乱させてしまい申し訳ありません。</t>
+        </is>
+      </c>
+      <c r="K348" s="3" t="n"/>
+      <c r="L348" s="3" t="n"/>
+      <c r="M348" s="3" t="inlineStr"/>
+      <c r="N348" s="3" t="inlineStr"/>
+      <c r="O348" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P348" s="3" t="inlineStr"/>
+      <c r="Q348" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R348" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="60" customHeight="1">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>EX-0348</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E349" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F349" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G349" s="3" t="inlineStr">
+        <is>
+          <t>I see where you're coming from, but I have some reservations.</t>
+        </is>
+      </c>
+      <c r="H349" s="3" t="inlineStr">
+        <is>
+          <t>お気持ちは分かりますが、いくつか懸念があります、という丁寧な反論表現。</t>
+        </is>
+      </c>
+      <c r="I349" s="3" t="inlineStr">
+        <is>
+          <t>I see where you're coming from, but I have some reservations about the timeline.</t>
+        </is>
+      </c>
+      <c r="J349" s="3" t="inlineStr">
+        <is>
+          <t>お気持ちは分かりますが、スケジュールについていくつか懸念があります。</t>
+        </is>
+      </c>
+      <c r="K349" s="3" t="n"/>
+      <c r="L349" s="3" t="n"/>
+      <c r="M349" s="3" t="inlineStr"/>
+      <c r="N349" s="3" t="inlineStr"/>
+      <c r="O349" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P349" s="3" t="inlineStr"/>
+      <c r="Q349" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R349" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="60" customHeight="1">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>EX-0349</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C350" s="3" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E350" s="3" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F350" s="3" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G350" s="3" t="inlineStr">
+        <is>
+          <t>With all due respect, I have to disagree.</t>
+        </is>
+      </c>
+      <c r="H350" s="3" t="inlineStr">
+        <is>
+          <t>恐れながら、意見が異なります、というフォーマルな反論表現。</t>
+        </is>
+      </c>
+      <c r="I350" s="3" t="inlineStr">
+        <is>
+          <t>With all due respect, I have to disagree — the data suggests otherwise.</t>
+        </is>
+      </c>
+      <c r="J350" s="3" t="inlineStr">
+        <is>
+          <t>恐れながら、意見が異なります。データは別のことを示唆しています。</t>
+        </is>
+      </c>
+      <c r="K350" s="3" t="n"/>
+      <c r="L350" s="3" t="n"/>
+      <c r="M350" s="3" t="inlineStr"/>
+      <c r="N350" s="3" t="inlineStr">
+        <is>
+          <t>「with all due respect」は敬意を示しつつ反対するクッション言葉。</t>
+        </is>
+      </c>
+      <c r="O350" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P350" s="3" t="inlineStr"/>
+      <c r="Q350" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R350" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="60" customHeight="1">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>EX-0350</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C351" s="3" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>提案,確認</t>
+        </is>
+      </c>
+      <c r="E351" s="3" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F351" s="3" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G351" s="3" t="inlineStr">
+        <is>
+          <t>Let's agree on the next checkpoint before we end.</t>
+        </is>
+      </c>
+      <c r="H351" s="3" t="inlineStr">
+        <is>
+          <t>終わる前に次の確認ポイントについて合意しましょう、という意味。</t>
+        </is>
+      </c>
+      <c r="I351" s="3" t="inlineStr">
+        <is>
+          <t>Let's agree on the next checkpoint before we end today's meeting.</t>
+        </is>
+      </c>
+      <c r="J351" s="3" t="inlineStr">
+        <is>
+          <t>今日のミーティングを終える前に、次の確認ポイントについて合意しましょう。</t>
+        </is>
+      </c>
+      <c r="K351" s="3" t="n"/>
+      <c r="L351" s="3" t="n"/>
+      <c r="M351" s="3" t="inlineStr"/>
+      <c r="N351" s="3" t="inlineStr"/>
+      <c r="O351" s="3" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="P351" s="3" t="inlineStr"/>
+      <c r="Q351" s="3" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R351" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R351"/>
+  <dimension ref="A1:R451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -26642,6 +26642,7081 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>EX-0351</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Let's start with a quick recap of last time.</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>前回のおさらいから始めましょう、という意味。プレゼンの冒頭で使う定番の切り出し方。</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Let's start with a quick recap of last time before we move on.</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>先に進む前に、前回のおさらいから始めましょう。</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Before we dive in, let's recap what we covered last time.</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>始める前に、前回扱った内容をおさらいしましょう。</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>Let's do a quick review of last time. / As a refresher, ...</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>EX-0352</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>I'll walk you through the key findings first.</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>まず主要な調査結果からご説明します、という意味。本題に入る前の前置き表現。</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>I'll walk you through the key findings first, then open it up for discussion.</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>まず主要な調査結果をご説明し、その後議論の時間を取ります。</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>Let me take you through the main findings.</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>EX-0353</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Feel free to interrupt if anything's unclear.</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>分かりにくい点があればいつでも遮ってください、という意味。質問を歓迎する姿勢を示す前置き。</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Feel free to interrupt if anything's unclear as we go along.</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>進めていく中で、分かりにくい点があればいつでも遮ってください。</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>Don't hesitate to stop me with questions.</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>EX-0354</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Let's take a closer look at this data point.</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>このデータについて詳しく見てみましょう、という意味。特定の数値やグラフに注目を促す表現。</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Let's take a closer look at this data point before moving to the next slide.</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>次のスライドに移る前に、このデータについて詳しく見てみましょう。</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>EX-0355</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>I'll circle back to this slide later.</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>このスライドには後で戻ります、という意味。話の流れを先に進めつつ、後で詳細に触れることを予告する表現。</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>I'll circle back to this slide later once we've covered the background.</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>背景を説明した後で、このスライドには改めて戻ります。</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>I'll come back to this point in a bit.</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>「circle back」は会議やメールでも頻出する「後で戻る・改めて確認する」の定番フレーズ。</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>EX-0356</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>To summarize what we've covered so far...</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>ここまでの内容をまとめると…という意味。中間まとめに入るときの定番の切り出し。</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>To summarize what we've covered so far, the project is on track but slightly over budget.</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>ここまでの内容をまとめると、プロジェクトは順調ですが予算はやや超過しています。</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>To recap what we've discussed...</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>EX-0357</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>I'd like to hand it over to my colleague for the next part.</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>ここからは同僚に引き継ぎます、という意味。プレゼンの担当交代時に使う表現。</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>I'd like to hand it over to my colleague for the next part of the presentation.</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>ここからのプレゼンは同僚に引き継ぎたいと思います。</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>I'll pass it over to Sarah from here.</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>EX-0358</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Let's not get too deep into the weeds here.</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>ここでは細部に入り込みすぎないようにしましょう、という意味。「in the weeds」は「細部・雑務に埋もれる」を表す口語表現。</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Let's not get too deep into the weeds here — I'll share the full details afterward.</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>ここでは細部に入り込みすぎないようにしましょう。詳細は後ほど共有します。</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>Let's not get bogged down in the details.</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>「in the weeds」はカジュアルな響きがあるため、フォーマルな場では「go into too much detail」に言い換えると無難。</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>EX-0359</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>I'll leave the technical Q&amp;A for after the session.</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>技術的な質疑は後のセッションに回します、という意味。専門的な質問を後回しにしたいときの表現。</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>I'll leave the technical Q&amp;A for after the session so we can keep this part high-level.</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>この部分は概要にとどめたいので、技術的な質疑は後のセッションに回します。</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>EX-0360</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>This next chart really drives the point home.</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>次のグラフがこの点を裏付けています、という意味。「drive the point home」は「主張を強く印象づける」の意味。</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>This next chart really drives the point home — revenue has doubled in two years.</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>次のグラフがこの点を裏付けています。売上は2年で倍増しました。</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>This next chart makes the case really clear.</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>EX-0361</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Thanks for picking up on such short notice.</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>急なお電話にもかかわらずありがとうございます、という意味。急な電話をかけた際の冒頭の一言。</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Thanks for picking up on such short notice — I know you're busy.</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>お忙しいところ、急なお電話にもかかわらずありがとうございます。</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>EX-0362</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>I'll need to check and call you right back.</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>確認してすぐに折り返します、という意味。即答できない場合の定番の返し。</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>I'll need to check and call you right back — give me five minutes.</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>確認してすぐに折り返します。5分ほどお時間をください。</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>Let me check on that and call you back.</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>EX-0363</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>You're coming through a bit faint.</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>少し声が遠いです、という意味。電話の音声が小さいときに使う表現。</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Sorry, you're coming through a bit faint. Could you speak up?</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>すみません、少し声が遠いです。もう少し大きな声でお願いできますか。</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>Your voice is a bit low on my end.</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>EX-0364</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Let me transfer this call to the right team.</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>このお電話を適切なチームにおつなぎします、という意味。担当部署に取り次ぐときの表現。</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Let me transfer this call to the right team who can help you with that.</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>その件でしたら、適切なチームにお電話をおつなぎします。</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>EX-0365</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Could you bear with me for one moment?</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>少々お待ちいただけますか、という意味。何かを確認している間に相手を待たせるときの丁寧な表現。</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Could you bear with me for one moment while I pull up your account?</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>アカウント情報を確認しますので、少々お待ちいただけますか。</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>Could you give me just a moment?</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>EX-0366</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>I think we have a bad connection.</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>電波が悪いようです、という意味。通話が聞き取りにくいときに使うカジュアルな表現。</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>I think we have a bad connection — let me call you back on a landline.</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>電波が悪いようなので、固定電話からかけ直しますね。</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>EX-0367</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>I'll send you a text with the details right after.</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>詳細は後ほどメッセージでお送りします、という意味。電話の後にテキストでフォローすることを伝える表現。</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>I'll send you a text with the details right after we hang up.</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>通話が終わったらすぐに、詳細をメッセージでお送りします。</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>EX-0368</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Apologies, I stepped away — could you repeat the last part?</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>失礼しました、最後の部分をもう一度お願いできますか、という意味。席を外していて聞き逃した際の丁寧な断り＋依頼。</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Apologies, I stepped away for a second — could you repeat the last part?</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>失礼しました、少し席を外していました。最後の部分をもう一度お願いできますか。</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>EX-0369</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Let's hold off on that until we have more data.</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>もっとデータが揃うまで保留にしましょう、という意味。判断材料が不足しているときに使う表現。</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Let's hold off on that until we have more data from the pilot.</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>パイロット版のデータが揃うまで、その件は保留にしましょう。</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>Let's park that until we know more.</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>EX-0370</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Can we get a show of hands on this?</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>この件、挙手で確認できますか、という意味。会議で簡易的に賛否や意見を確認するときの表現。</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Can we get a show of hands on this before we decide?</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>決める前に、この件について挙手で確認できますか。</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>EX-0371</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>I want to make sure we're not missing anyone's input.</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>誰の意見も漏らさないようにしたいです、という意味。発言していない参加者に配慮する場面で使う表現。</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>I want to make sure we're not missing anyone's input before we wrap up.</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>終える前に、誰の意見も漏らさないようにしたいです。</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>EX-0372</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Let's put a pin in that and move on.</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>それは一旦保留にして先に進みましょう、という意味。「put a pin in it」は「一旦保留する」を表すカジュアルな慣用表現。</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Let's put a pin in that and move on to the next agenda item.</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>それは一旦保留にして、次の議題に進みましょう。</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>Let's table that for now.</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>EX-0373</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Who owns this action item?</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>このタスクの担当は誰ですか、という意味。アクションアイテムの責任者を確認する定番表現。</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Who owns this action item going forward?</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>今後、このタスクの担当は誰になりますか。</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>EX-0374</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Let's not spend too much time on this one.</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>この件にあまり時間をかけすぎないようにしましょう、という意味。議論を効率よく進めたいときに使う表現。</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Let's not spend too much time on this one — we have a lot to cover.</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>この件にあまり時間をかけすぎないようにしましょう。他にも議題がたくさんあります。</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>EX-0375</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>I think we've beaten this topic to death.</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>この話題はもう十分に議論しましたね、という意味。「beat a topic to death」は「話題を議論し尽くす」を表す口語表現。</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>I think we've beaten this topic to death — let's move on.</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>この話題はもう十分に議論しましたね。次に進みましょう。</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>ややくだけた表現なので、フォーマルな会議では「I think we've covered this thoroughly」の方が無難。</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>EX-0376</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Can we sync up briefly after this?</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>この後、少し打ち合わせできますか、という意味。会議の後で個別に話したいときの表現。</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Can we sync up briefly after this to go over the details?</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>詳細を確認するため、この後少し打ち合わせできますか。</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Can we grab a few minutes after this?</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>EX-0377</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Let's not rush into anything just yet.</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>まだ急いで決めないようにしましょう、という意味。交渉で拙速な合意を避けたいときの表現。</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Let's not rush into anything just yet — we should weigh our options.</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>まだ急いで決めないようにしましょう。選択肢をよく検討すべきです。</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>EX-0378</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>We're open to discussing the terms further.</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>条件についてはさらに話し合う余地があります、という意味。交渉継続の意思を示す表現。</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>We're open to discussing the terms further if that helps move things along.</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>話を前進させるためであれば、条件についてはさらに話し合う余地があります。</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>EX-0379</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>That's a reasonable ask, but let me check internally.</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>それは妥当な要望ですが、社内で確認させてください、という意味。即答を避けつつ相手の要望を尊重する表現。</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>That's a reasonable ask, but let me check internally before I commit.</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>それは妥当な要望ですが、確約する前に社内で確認させてください。</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>EX-0380</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>We'd need to see some movement on your end too.</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>そちらにも歩み寄っていただく必要があります、という意味。一方的な譲歩を避けたいときの表現。</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>We'd need to see some movement on your end too if we're going to close this deal.</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>この取引をまとめるには、そちらにも歩み寄っていただく必要があります。</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>EX-0381</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Let's put this in writing once we agree.</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>合意したら書面にまとめましょう、という意味。口頭合意を正式な文書に落とし込む提案。</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Let's put this in writing once we agree on the final numbers.</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>最終的な数字に合意したら、書面にまとめましょう。</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>EX-0382</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>I don't want to leave money on the table.</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>損はしたくないんです、という意味。「leave money on the table」は「得られたはずの利益を逃す」を表す慣用表現。</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>I don't want to leave money on the table, so let's negotiate a bit more.</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>損はしたくないので、もう少し交渉させてください。</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>EX-0383</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Would it be too much to ask for an extension?</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>延長をお願いするのは無理を言い過ぎでしょうか、という意味。丁寧に延長を依頼する表現。</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Would it be too much to ask for an extension until Friday?</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>金曜日までの延長をお願いするのは無理を言い過ぎでしょうか。</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Would it be possible to get a bit more time?</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>EX-0384</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>I'm afraid my plate is full this week.</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>今週は手一杯です、という意味。忙しくて対応できないことを丁寧に伝える表現。</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>I'm afraid my plate is full this week, but I can help next week.</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>今週は手一杯ですが、来週であればお手伝いできます。</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>I've got a lot on my plate this week.</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>EX-0385</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Could you loop me in when it's ready?</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>準備ができたら私にも共有してもらえますか、という意味。進捗を後で共有してほしいときの表現。</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Could you loop me in when it's ready? I'd love to take a look.</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>準備ができたら私にも共有してもらえますか。ぜひ見てみたいです。</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Could you keep me posted once it's done?</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>EX-0386</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>I'll have to check my availability first.</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>まず自分の空き状況を確認しないといけません、という意味。即答を避けるときの表現。</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>I'll have to check my availability first before I can confirm.</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>確定する前に、まず自分の空き状況を確認しないといけません。</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>EX-0387</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>I really wish I could, but the timing's off.</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>本当にそうしたいのですが、タイミングが合いません、という意味。丁寧に断るときの表現。</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>I really wish I could, but the timing's off with my current workload.</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>本当にそうしたいのですが、今の業務量だとタイミングが合いません。</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>EX-0388</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Would you be able to squeeze this in somehow?</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>なんとかこれを組み込んでいただけますか、という意味。忙しい相手に無理を承知でお願いする表現。</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Would you be able to squeeze this in somehow before the deadline?</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>締め切り前になんとかこれを組み込んでいただけますか。</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>EX-0389</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>How's everything going on your end?</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>そちらは順調ですか、という意味。相手の近況を尋ねるカジュアルな表現。</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>How's everything going on your end these days?</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>最近、そちらは順調ですか。</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>EX-0390</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>It's been ages!</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>久しぶりですね、という意味。しばらく会っていなかった相手への挨拶。</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>It's been ages! How have you been?</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>久しぶりですね！お元気でしたか。</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Long time no see!</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>EX-0391</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>I could really go for some coffee right about now.</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>今すぐコーヒーが飲みたい気分です、という意味。軽い雑談の一言。</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>I could really go for some coffee right about now. Want to grab one?</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>今すぐコーヒーが飲みたい気分です。一緒にどうですか。</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>EX-0392</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Work's been keeping me on my toes lately.</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>最近仕事に気を抜けない状態です、という意味。「on one's toes」は「気を抜けない・緊張した状態」を表す表現。</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Work's been keeping me on my toes lately, but it's a good kind of busy.</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>最近仕事に気を抜けない状態ですが、良い意味で忙しいです。</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>EX-0393</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Same old, same old.</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>相変わらずです、という意味。「最近どう？」と聞かれたときの軽い返答。</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>"How's it going?" "Same old, same old."</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>「調子どう？」「相変わらずだよ」</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>EX-0394</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>That takes me back!</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>懐かしいですね、という意味。昔を思い出させるものに出会ったときの表現。</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>That takes me back! I haven't heard that song in years.</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>懐かしいですね！この曲、何年も聞いていませんでした。</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>EX-0395</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Apologies for the back-and-forth on this.</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>このやり取りが続いてしまい申し訳ありません、という意味。何度もメールが往復していることを詫びる表現。</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Apologies for the back-and-forth on this — let's finalize the details on a call instead.</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>このやり取りが続いてしまい申し訳ありません。詳細は通話で確定させましょう。</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>EX-0396</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Please let us know should anything change on your side.</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>そちらで何か変更があればお知らせください、という意味。状況変化の連絡を依頼する丁寧な表現。</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Please let us know should anything change on your side before the deadline.</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>締め切り前にそちらで何か変更があれば、お知らせください。</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>EX-0397</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>I've summarized the key points below for convenience.</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>分かりやすいよう要点を以下にまとめました、という意味。長いメールの冒頭で使う表現。</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>I've summarized the key points below for convenience.</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>分かりやすいよう、要点を以下にまとめました。</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>EX-0398</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>We're happy to schedule a call to discuss further.</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>さらに話し合うためのお電話も承ります、という意味。メールでのやり取りに加えて通話を提案する表現。</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>We're happy to schedule a call to discuss further at your convenience.</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>ご都合のよいときに、さらに話し合うためのお電話も承ります。</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>EX-0399</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Thank you for bringing this to our attention.</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>この件をお知らせいただきありがとうございます、という意味。問題やミスの指摘に対して感謝を述べる表現。</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Thank you for bringing this to our attention. We'll look into it right away.</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>この件をお知らせいただきありがとうございます。すぐに確認いたします。</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>EX-0400</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>I'll follow up once I hear back from the team.</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>チームから返答があり次第、改めてご連絡します、という意味。社内確認待ちであることを伝える表現。</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>I'll follow up once I hear back from the team on this.</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>この件についてチームから返答があり次第、改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>EX-0401</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>bring something to the table</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>（価値ある提案・強みを）提供する</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>She brings a lot of experience to the table.</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>彼女は豊富な経験を持ち込んでくれます。</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>What can our team bring to the table for this project?</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>このプロジェクトで私たちのチームは何を提供できるでしょうか。</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>contribute</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>EX-0402</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>call the shots</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>決定権を持つ、仕切る</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Ultimately, the client calls the shots on the final design.</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>最終的にはクライアントが最終デザインの決定権を持ちます。</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Who's calling the shots on this project?</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>このプロジェクトの決定権は誰が持っていますか。</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>be in charge</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>EX-0403</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>keep something in mind</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>〜を心に留めておく、考慮に入れる</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Please keep in mind that the budget is limited.</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>予算が限られていることを念頭に置いてください。</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>We'll keep your feedback in mind for the next version.</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>次のバージョンでは、いただいたフィードバックを考慮します。</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>bear in mind</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>EX-0404</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>weigh in on something</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>意見を述べる</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Would you like to weigh in on this before we decide?</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>決定する前に、これについて意見をいただけますか。</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Everyone was invited to weigh in on the new policy.</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>全員が新しい方針について意見を述べるよう求められました。</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>give input</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>EX-0405</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>hash out the details</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>細部を詰める</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Let's schedule a call to hash out the details.</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>細部を詰めるための打ち合わせを設定しましょう。</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>We still need to hash out a few details before signing.</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>署名の前にいくつか細部を詰める必要があります。</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>iron out the details</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>EX-0406</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>reach a stalemate</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>行き詰まる、膠着状態になる</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>The negotiations reached a stalemate over pricing.</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>交渉は価格を巡って行き詰まりました。</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>We seem to have reached a stalemate on this issue.</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>この問題については行き詰まってしまったようです。</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>hit a deadlock</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>EX-0407</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>play devil's advocate</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>あえて反対意見を言う</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Let me play devil's advocate for a second — what if the launch is delayed?</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>あえて反対意見を言わせてください。もし発売が遅れたらどうしますか。</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>She often plays devil's advocate to stress-test our ideas.</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>彼女は私たちの案を検証するため、よく意図的に反対意見を出します。</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>EX-0408</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>steer the conversation</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>話の方向を導く</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>He steered the conversation back to the main agenda.</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>彼は話を本来の議題に戻す方向に導きました。</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Let's steer the conversation toward next steps.</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>話を次のステップの方向に進めましょう。</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>EX-0409</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>go off on a tangent</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>話が脱線する</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Sorry, I went off on a tangent there. Let's get back to the agenda.</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>すみません、話が脱線しました。議題に戻りましょう。</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>The discussion kept going off on a tangent.</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>議論はずっと脱線し続けていました。</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>EX-0410</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>wrap something up</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>〜を締めくくる、終わらせる</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Let's wrap this meeting up in the next five minutes.</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>あと5分でこの会議を締めくくりましょう。</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>I'll wrap up my part and hand it over to Tom.</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>自分のパートを締めくくって、トムに引き継ぎます。</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>finish up</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>EX-0411</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>rubber-stamp a decision</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>（十分な検討なしに）機械的に承認する</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>The board simply rubber-stamped the decision without much discussion.</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>取締役会はあまり議論せずにその決定を機械的に承認しました。</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>We shouldn't just rubber-stamp this proposal.</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>この提案を単に機械的に承認すべきではありません。</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>やや否定的なニュアンスを含む表現</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>EX-0412</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>put something to a vote</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>採決にかける</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Let's put this proposal to a vote.</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>この提案を採決にかけましょう。</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>The committee put the budget plan to a vote.</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>委員会は予算計画を採決にかけました。</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>EX-0413</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>as per my last email</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>前回のメールでお伝えした通り</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>As per my last email, the deadline has been moved to Friday.</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>前回のメールでお伝えした通り、締め切りは金曜に変更されました。</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>As per my last email, please find the updated file attached.</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>前回のメールでお伝えした通り、更新済みファイルを添付しております。</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>as previously mentioned</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>EX-0414</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>per the attached</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>添付の通り</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Per the attached, our new pricing takes effect next month.</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>添付の通り、新価格は来月から適用されます。</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Per the attached invoice, payment is due by the 15th.</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>添付の請求書の通り、お支払いは15日までとなります。</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>EX-0415</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>cc someone on an email</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>（人を）CCに入れる</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>I've cc'd the finance team on this email.</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>このメールに経理チームをCCしています。</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Could you cc me on any updates going forward?</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>今後の更新について私もCCに入れていただけますか。</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>口語では動詞として使う（cc'd = past tense）</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>EX-0416</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>bcc someone</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>（人を）BCCに入れる</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>I'll bcc my manager just for visibility.</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>念のため上司をBCCに入れておきます。</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Please don't forget to bcc HR on this notice.</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>この通知には人事部をBCCに入れるのを忘れないでください。</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>EX-0417</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>flag an email as urgent</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>メールを緊急扱いにする</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>I flagged the email as urgent since we need a response today.</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>本日中の返信が必要なため、そのメールを緊急扱いにしました。</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Please flag it as urgent if it needs immediate attention.</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>至急対応が必要な場合は緊急扱いにしてください。</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>mark as urgent</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>EX-0418</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>send a reminder email</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>リマインドメールを送る</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>I'll send a reminder email a day before the deadline.</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>締め切りの前日にリマインドメールを送ります。</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Could you send a reminder email to everyone who hasn't RSVP'd?</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>まだ出欠回答をしていない方にリマインドメールを送っていただけますか。</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>EX-0419</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>reply-all by mistake</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>誤って全員に返信する</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Sorry, I replied-all by mistake on the last email.</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>先ほどのメール、誤って全員に返信してしまいすみません。</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Please be careful not to reply-all by mistake on this thread.</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>このスレッドで誤って全員に返信しないよう注意してください。</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>EX-0420</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>draft an email</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>メールの下書きを作る</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>I've drafted an email to the client — could you review it before I send it?</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>クライアント宛のメールを下書きしました。送る前に確認いただけますか。</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Let me draft an email and share it with you first.</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>まずメールを下書きして共有します。</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>EX-0421</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>proofread an email before sending</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>送信前にメールを校正する</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Always proofread an email before sending it to a client.</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>クライアントに送る前は必ずメールを校正してください。</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>I proofread the email twice before hitting send.</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>送信ボタンを押す前にそのメールを2回校正しました。</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>EX-0422</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>mark an email as read</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>メールを既読にする</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>I accidentally marked the email as read without opening it.</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>開かずに誤ってそのメールを既読にしてしまいました。</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Could you mark this thread as read once you've reviewed it?</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>確認が終わったらこのスレッドを既読にしていただけますか。</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>EX-0423</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>put someone on speakerphone</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>スピーカーホンにする</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Do you mind if I put you on speakerphone? My colleague would like to join.</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>スピーカーホンにしてもよろしいですか。同僚も参加したいそうです。</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>I put the call on speakerphone so the whole team could listen.</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>チーム全員が聞けるよう、その通話をスピーカーホンにしました。</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>EX-0424</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>leave a voicemail</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>ボイスメールを残す</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>I'll leave a voicemail if he doesn't pick up.</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>彼が出なければボイスメールを残しておきます。</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>She left a voicemail asking me to call her back.</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>彼女は折り返し電話するようボイスメールを残しました。</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>EX-0425</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>return a phone call</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>電話を折り返す</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>I'll return your call as soon as I'm free.</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>手が空き次第、折り返しお電話します。</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Could you return my call sometime this afternoon?</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>今日の午後、いつでもいいので折り返しお電話いただけますか。</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>call back</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>EX-0426</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>get cut off</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>（電話が）切れる</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Sorry, we got cut off earlier — where were we?</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>すみません、さっき電話が切れてしまいました。どこまで話しましたっけ。</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>The call got cut off right before we finished.</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>終わる直前に電話が切れてしまいました。</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>get disconnected</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>EX-0427</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>dial the wrong number</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>間違い電話をかける</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>I'm sorry, I think I dialed the wrong number.</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>すみません、間違い電話をかけてしまったようです。</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>It looks like she dialed the wrong number by mistake.</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>彼女は誤って間違い電話をかけてしまったようです。</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>EX-0428</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>hold the line</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>電話を切らずに待つ</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Could you please hold the line for a moment?</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>少々そのままお待ちいただけますか。</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Please hold the line while I transfer your call.</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>お電話をお繋ぎしますので、そのままお待ちください。</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>hold on</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>EX-0429</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>make a case for something</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>〜の主張を裏付ける、論拠を示す</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>I'd like to make a case for expanding into the Asian market.</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>アジア市場への進出について論拠を示したいと思います。</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>This slide makes a strong case for the new strategy.</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>このスライドは新戦略について強い論拠を示しています。</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>EX-0430</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>back up a claim with data</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>データで主張を裏付ける</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Let me back up this claim with some recent data.</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>この主張を最近のデータで裏付けさせてください。</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>It's important to back up your claims with solid data.</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>主張は確かなデータで裏付けることが重要です。</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>EX-0431</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>draw a conclusion</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>結論を導き出す</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Based on this data, we can draw a clear conclusion.</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>このデータに基づけば、明確な結論を導き出せます。</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Let's not draw any conclusions until we have all the results.</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>全ての結果が出るまで結論を出すのは控えましょう。</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>EX-0432</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>give a rundown of something</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>〜の概要を説明する</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Let me give you a quick rundown of today's agenda.</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>本日の議題について簡単に概要をご説明します。</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>I'll give a rundown of the project's progress so far.</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>これまでのプロジェクトの進捗について概要をお伝えします。</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>give an overview</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>EX-0433</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>field questions from the audience</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>聴衆からの質問に答える</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>I'll field questions from the audience after the presentation.</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>発表の後、会場からの質問にお答えします。</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>She fielded several tough questions from the audience.</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>彼女は会場からのいくつかの厳しい質問に答えました。</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>EX-0434</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>walk someone through a chart</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>（人に）図表を見ながら説明する</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Let me walk you through this chart step by step.</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>この図表を一つずつご説明していきます。</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>I'll walk the client through the sales chart during the call.</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>通話中にクライアントに売上グラフを説明します。</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>EX-0435</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>drive a hard bargain</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>強気の交渉をする</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>You drive a hard bargain, but I think we can agree on this.</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>強気な交渉をされますね、でもこれで合意できると思います。</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Their team drove a hard bargain during the negotiations.</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>彼らのチームは交渉中、強気な姿勢を崩しませんでした。</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>EX-0436</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>come to terms</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>条件について合意する</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>We finally came to terms after weeks of negotiation.</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>数週間の交渉の末、ついに条件面で合意しました。</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>I hope we can come to terms that work for both sides.</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>双方にとって良い条件で合意できることを願っています。</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>reach an agreement</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>EX-0437</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>haggle over the price</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>価格について値切り交渉をする</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Let's not haggle over the price too much — time is limited.</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>あまり価格交渉に時間をかけすぎないようにしましょう。時間が限られています。</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>They spent an hour haggling over the price.</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>彼らは1時間かけて価格交渉をしました。</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>EX-0438</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>strike a balance</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>バランスを取る</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>We need to strike a balance between cost and quality.</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>コストと品質の間でバランスを取る必要があります。</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>It's about striking a balance that satisfies both parties.</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>双方が納得できるバランスを取ることが重要です。</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>EX-0439</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>give and take</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>譲り合い、互譲</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Negotiation is all about give and take.</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>交渉とは譲り合いそのものです。</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>There needs to be some give and take on both sides.</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>双方に多少の譲り合いが必要です。</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>EX-0440</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>break the deadlock</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>行き詰まりを打開する</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>This new proposal might help break the deadlock.</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>この新しい提案が行き詰まりを打開する助けになるかもしれません。</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>We need a fresh idea to break the deadlock in these talks.</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>この交渉の行き詰まりを打開するには新しいアイデアが必要です。</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>EX-0441</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>set the terms</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>条件を定める</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>The client wants to set the terms before we begin.</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>クライアントは開始前に条件を定めたいと考えています。</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Let's set the terms clearly before drafting the contract.</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>契約書を作成する前に条件をはっきり定めましょう。</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>EX-0442</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>finalize the terms of a contract</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>契約条件を最終決定する</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>We hope to finalize the terms of the contract by Friday.</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>金曜までに契約条件を最終決定したいと考えています。</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Both parties agreed to finalize the terms of the contract next week.</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>両者は来週、契約条件を最終決定することに合意しました。</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>EX-0443</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>take someone up on an offer</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>（申し出を）受け入れる</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>I'll take you up on that offer, thank you.</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>そのお申し出、ぜひ受けさせていただきます。ありがとうございます。</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>We'd like to take you up on your proposal to extend the deadline.</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>締め切り延長のご提案、ありがたくお受けしたいと思います。</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>EX-0444</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>turn down a request</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>依頼を断る</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>I'm sorry, but we have to turn down this request.</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>申し訳ありませんが、このご依頼はお断りせざるを得ません。</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>The manager turned down the request due to budget constraints.</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>予算上の制約により、マネージャーはその依頼を断りました。</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>decline a request</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>EX-0445</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>put in a request</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>依頼を出す、申請する</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>I've put in a request for additional staff.</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>追加の人員について申請を出しました。</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Could you put in a request for the new equipment?</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>新しい機材について申請を出していただけますか。</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>EX-0446</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>grant an exception</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>例外を認める</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>We're willing to grant an exception in this case.</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>今回のケースでは例外を認める用意があります。</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Management rarely grants exceptions to this policy.</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>経営陣がこの方針に例外を認めることはめったにありません。</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>EX-0447</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>make an exception</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>特例を作る</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Could you make an exception just this once?</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>今回だけ特例にしていただけないでしょうか。</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>We don't usually do this, but we'll make an exception for you.</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>通常はこのようなことはしないのですが、あなたのために特例を作ります。</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>EX-0448</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>make small talk</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>雑談をする</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>We made some small talk before the meeting started.</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>会議が始まる前に少し雑談をしました。</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>He's good at making small talk with clients.</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>彼はクライアントと雑談するのが上手です。</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>EX-0449</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>break the ice</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>場を和ませる</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Let's start with a quick icebreaker to break the ice.</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>アイスブレイクから始めて場を和ませましょう。</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>She told a joke to break the ice at the start of the meeting.</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>彼女は会議の冒頭で場を和ませるために冗談を言いました。</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>EX-0450</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>TOEIC表現</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>hit it off with someone</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>（人と）意気投合する</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>I really hit it off with the new client.</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>新しいクライアントとすっかり意気投合しました。</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>They hit it off right away during the conference.</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>彼らはカンファレンス中にすぐ意気投合しました。</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S451"/>
+  <dimension ref="A1:S551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -34322,6 +34322,7436 @@
         </is>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>EX-0451</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Could we park this discussion and revisit it tomorrow?</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>この話は一旦保留にして、明日また話しましょうか</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Could we park this discussion and revisit it tomorrow? We're running out of time.</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>この話は一旦保留にして明日また話しましょうか。時間が足りなくなってきました。</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Sure, let's park it and move to the next agenda item.</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>そうですね、保留にして次の議題に移りましょう。</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>park =「一時的に脇に置く」という意味の口語表現。table thisと似た意味だが、より柔らかい響き。</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>EX-0452</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>I'm not entirely convinced this is the right approach.</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>これが正しいやり方だとは、正直まだ納得しきれていません</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>I'm not entirely convinced this is the right approach, to be honest.</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>正直なところ、これが正しいやり方だとは納得しきれていません。</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Fair enough — what would you suggest instead?</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>なるほど、では代わりにどうすればいいと思いますか？</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>I don't agree より柔らかく、反対を婉曲に伝える定番の言い回し。</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>EX-0453</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Just to make sure we're aligned, could you recap the decision?</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>認識を合わせるために、決定事項を要約してもらえますか</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Just to make sure we're aligned, could you recap the decision we just made?</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>認識を合わせるために、今決まったことを要約してもらえますか。</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Sure — we're moving the launch date to next month.</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>はい、発売日を来月に変更することになりました。</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>会議の終わりに認識のズレを防ぐための定番フレーズ。</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>EX-0454</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>You and me both.</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>私も全く同じです</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>"I could really use a vacation." "You and me both."</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>「本当に休暇が欲しいよ」「私もまったく同じ気持ちです」</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>相手の発言に強く共感するときのカジュアルな相槌。</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>EX-0455</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Would you mind taking a quick look at the attached draft?</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>添付の下書きにさっと目を通していただけますか</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Would you mind taking a quick look at the attached draft before Friday?</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>金曜日までに添付の下書きにさっと目を通していただけますか。</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Not at all, I'll get back to you by tomorrow.</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>もちろんです、明日までにお返事しますね。</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Would you mind ~ing? は丁寧な依頼表現の定番。承諾の返事は"Not at all"（構いません）となる点に注意。</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>EX-0456</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>メール,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>I'm afraid this will have to wait until next quarter.</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>申し訳ありませんが、これは来四半期まで待つ必要がありそうです</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>I'm afraid this project will have to wait until next quarter due to budget constraints.</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>予算の都合上、このプロジェクトは来四半期まで待つ必要がありそうです。</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>I'm afraid ~ は悪いニュースを柔らかく伝える定番の前置き表現。</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>EX-0457</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Just to confirm, you said the meeting is at 3, not 4, right?</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>確認ですが、会議は4時ではなく3時とおっしゃいましたよね</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Just to confirm, you said the meeting is at 3, not 4, right? I want to make sure I have it in my calendar correctly.</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>確認ですが、会議は4時ではなく3時とおっしゃいましたよね。カレンダーに正しく入れておきたいので。</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>That's right, 3 o'clock sharp.</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>はい、3時ちょうどです。</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>電話口で聞き間違いを防ぐための定番の確認フレーズ。</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>EX-0458</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Let me propose a slightly different angle on this.</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>これについて少し違う切り口を提案させてください</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Let me propose a slightly different angle on this before we finalize the plan.</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>計画を確定する前に、少し違う切り口を提案させてください。</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>「別の視点・切り口」を提示するときのフォーマルな前置き表現。</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>EX-0459</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>I have to push back on that a little.</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>少しその点には異議を唱えさせてください</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>I have to push back on that a little — the timeline seems unrealistic.</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>少しその点には異議を唱えさせてください。そのスケジュールは現実的ではないように思います。</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>push back on ~ は「〜に対して異議を唱える、反発する」という口語的だが定番のビジネス表現。</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>EX-0460</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Let's not lose momentum on this.</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>この勢いを失わないようにしましょう</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>We've made great progress — let's not lose momentum on this.</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>大きく前進しましたね。この勢いを失わないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>プロジェクトの勢いを維持しようと呼びかける前向きな表現。</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>EX-0461</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Can we sanity-check these numbers before sending them out?</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>送る前にこの数字が正しいか一応確認できますか</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Can we sanity-check these numbers before sending them out to the client?</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>クライアントに送る前にこの数字が正しいか一応確認できますか。</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>sanity check =「一応の妥当性チェック」を意味するカジュアルなビジネス表現。</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>EX-0462</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>I don't want to put words in your mouth, but is that what you meant?</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>勝手に決めつけたくはないのですが、そういう意味でおっしゃいましたか</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>I don't want to put words in your mouth, but is that what you meant by 'flexible hours'?</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>勝手に決めつけたくはないのですが、「柔軟な勤務時間」とはそういう意味でおっしゃいましたか。</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>相手の発言を自分なりに解釈して確認する際の丁寧な前置き。</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>EX-0463</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Let's not put all our eggs in one basket.</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>一つに賭けすぎるのはやめましょう</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Let's not put all our eggs in one basket — we should diversify our suppliers.</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>一つに賭けすぎるのはやめましょう。サプライヤーを分散させるべきです。</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>リスクを一箇所に集中させないよう助言する定番のことわざ表現。</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>EX-0464</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>I'll take that as a yes.</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>それは了承ということで受け取りますね</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>You didn't say no, so I'll take that as a yes.</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>反対しなかったので、了承ということで受け取りますね。</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>相手の曖昧な返事を軽く念押しして確認するカジュアルな表現。</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>EX-0465</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Let's not reinvent the wheel here.</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>一からやり直す必要はないでしょう</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Let's not reinvent the wheel here — we can adapt last year's template.</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>一からやり直す必要はないでしょう。昨年のテンプレートを応用できます。</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>既にある方法を活かそうと提案する際の定番の慣用表現。</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>EX-0466</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>I appreciate you being upfront about this.</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>率直に伝えてくれてありがたいです</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>I appreciate you being upfront about this — it makes planning much easier.</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>率直に伝えてくれてありがたいです。おかげで計画が立てやすくなります。</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>相手の正直さ・率直さに感謝を示す表現。</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>EX-0467</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Can we agree to disagree on this point and move on?</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>この点については意見の相違を認めて先に進みませんか</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Can we agree to disagree on this point and move on to the next item?</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>この点については意見の相違を認めて次の議題に進みませんか。</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>対立が解消しない議論を切り上げるための定番表現。</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>EX-0468</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>I'll defer to the experts on this one.</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>この件については専門家の判断に従います</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>I'll defer to the experts on this one since it's outside my area.</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>この件は自分の専門外なので、専門家の判断に従います。</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>自分より詳しい人の判断を尊重するときの丁寧な表現。</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>EX-0469</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Let's not jump to conclusions before we have all the facts.</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>すべての事実がそろう前に結論を急がないようにしましょう</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Let's not jump to conclusions before we have all the facts.</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>すべての事実がそろう前に結論を急がないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>早合点を戒める定番のイディオム。</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>EX-0470</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>I owe you an explanation for what happened.</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>何が起きたのか説明する義務があると思います</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>I owe you an explanation for what happened at yesterday's meeting.</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>昨日の会議で何が起きたのか、説明する義務があると思います。</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>自分の非を認め、経緯を説明する前に使う前置き表現。</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>EX-0471</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>会議,電話</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Let's circle the wagons on this before the client call.</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>クライアントとの電話の前に一度足並みを揃えましょう</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Let's circle the wagons on this before the client call this afternoon.</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>今日午後のクライアントとの電話の前に一度足並みを揃えましょう。</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>チーム内で結束・意思統一を図ろうと呼びかける口語的な表現。</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>EX-0472</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>I don't mean to nitpick, but this figure looks off.</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>細かいことを言うようですが、この数字はおかしい気がします</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>I don't mean to nitpick, but this figure looks off compared to last month.</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>細かいことを言うようですが、この数字は先月と比べておかしい気がします。</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>細かい指摘をする際の前置きとして使う定番フレーズ。</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>EX-0473</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Can we take a quick straw poll on this?</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>ここで簡単な意向確認をしてもいいですか</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Can we take a quick straw poll on this before we vote formally?</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>正式に投票する前に、ここで簡単な意向確認をしてもいいですか。</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>straw poll =正式な決定の前段階として行う略式の意向調査。</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>EX-0474</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Let's not beat around the bush — what's the real issue here?</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>遠回しに言うのはやめて、本当の問題は何ですか</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Let's not beat around the bush — what's the real issue here?</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>遠回しに言うのはやめて、本当の問題は何なのか教えてください。</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>本題をはっきり聞くために使う直接的な表現。</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>EX-0475</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>I'll hold you to that.</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>その言葉、忘れないでくださいね</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>You said you'd finish it by Friday — I'll hold you to that.</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>金曜までに終わらせると言いましたね、その言葉、忘れないでくださいね。</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>相手の約束を念押しして確認する軽いニュアンスの表現。</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>EX-0476</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Let's not drag this out any longer.</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>これ以上長引かせるのはやめましょう</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Let's not drag this out any longer — can we make a decision today?</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>これ以上長引かせるのはやめましょう。今日中に決められませんか。</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>議論を早く終わらせたいときに使う表現。</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>EX-0477</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>I'm on the fence about this one.</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>これについてはまだ決めかねています</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>I'm on the fence about this one — could you give me a day to think it over?</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>これについてはまだ決めかねています。一日考える時間をいただけますか。</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>賛成でも反対でもなく迷っている状態を表す定番のイディオム。</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>EX-0478</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>We should be on the same wavelength before the client meeting.</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>クライアントとの打ち合わせ前に、認識を合わせておくべきです</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>We should be on the same wavelength before the client meeting starts.</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>クライアントとの打ち合わせが始まる前に、認識を合わせておくべきです。</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>考え方や認識が一致していることを表すやや口語的な表現。</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>EX-0479</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>会議,電話</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Let me play it back to you to make sure I got it right.</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>正しく理解できたか、私の理解を確認させてください</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Let me play it back to you to make sure I got it right: we're pushing the deadline to Friday.</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>正しく理解できたか確認させてください。締め切りを金曜日に延ばす、ということですね。</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>相手の説明を自分の言葉で要約して確認する表現。</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>EX-0480</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>I'll leave that call up to you.</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>その判断はあなたに任せます</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>I'll leave that call up to you since you know the client better.</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>クライアントのことをよくご存知なので、その判断はあなたに任せます。</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>「call」は口語で「判断・決定」を意味する。</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>EX-0481</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Let's not overthink this.</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>あまり考えすぎないようにしましょう</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Let's not overthink this — we can always adjust later.</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>あまり考えすぎないようにしましょう。後で調整もできますし。</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>過度に慎重になりすぎないよう促すカジュアルな表現。</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>EX-0482</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>I'll need a second pair of eyes on this before I send it.</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>送る前にもう一人に確認してもらいたいです</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>I'll need a second pair of eyes on this before I send it to the client.</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>クライアントに送る前に、もう一人に確認してもらいたいです。</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>自分以外の視点でチェックしてほしいときの定番の言い回し。</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>EX-0483</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Let's not lose sleep over this.</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>このことで思い悩みすぎないようにしましょう</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>It's a minor issue, so let's not lose sleep over this.</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>小さな問題なので、思い悩みすぎないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>過度に心配しないよう相手を励ますイディオム。</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>EX-0484</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>I might be missing something, but could you walk me through this again?</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>何か見落としているかもしれませんが、もう一度説明していただけますか</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>I might be missing something, but could you walk me through this again from the top?</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>何か見落としているかもしれませんが、もう一度最初から説明していただけますか。</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>理解が追いついていないことを謙虚に伝えつつ再説明を求める表現。</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>EX-0485</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Let's not put the horse before the cart on this one.</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>この件は順序を間違えないようにしましょう</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Let's not put the horse before the cart — we need budget approval before hiring.</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>この件は順序を間違えないようにしましょう。採用の前に予算承認が必要です。</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>put the cart before the horseの慣用句を用いた「順序を間違えるな」という表現。</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>EX-0486</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>I'll flag it if anything changes on my end.</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>こちらで何か変更があれば知らせます</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>I'll flag it right away if anything changes on my end.</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>こちらで何か変更があれば、すぐに知らせます。</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>何か変化があれば連絡するという約束を表す表現。</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>EX-0487</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Let's not let perfect be the enemy of good.</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>完璧を求めすぎて前に進めなくならないようにしましょう</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Let's not let perfect be the enemy of good — we can ship this version and iterate.</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>完璧を求めすぎて前に進めなくならないようにしましょう。このバージョンをリリースして改善していけます。</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>完璧主義が進行を妨げないよう促す有名な格言。</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>EX-0488</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>I can't promise anything, but I'll see what I can do.</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>約束はできませんが、できることはやってみます</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>I can't promise anything, but I'll see what I can do about the deadline.</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>約束はできませんが、締め切りについてできることはやってみます。</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>明確な約束を避けつつ前向きな姿勢を示す表現。</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>EX-0489</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Let's touch on that briefly before we wrap up.</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>終わる前にそれについて少し触れておきましょう</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Let's touch on that briefly before we wrap up today's meeting.</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>今日の会議を終える前に、それについて少し触れておきましょう。</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>本格的に論じる時間はないが軽く触れておきたいときに使う表現。</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>EX-0490</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>I don't want to speak out of turn, but I have a concern.</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>出過ぎたことを言うようですが、懸念があります</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>I don't want to speak out of turn, but I have a concern about the timeline.</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>出過ぎたことを言うようですが、スケジュールについて懸念があります。</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>発言の立場をわきまえつつ、意見を述べる際の丁寧な前置き。</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>EX-0491</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Let's keep the lines of communication open.</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>引き続き連絡を取り合いましょう</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Let's keep the lines of communication open as the project progresses.</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>プロジェクトが進む中でも、引き続き連絡を取り合いましょう。</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>継続的な情報共有を呼びかける定番表現。</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>EX-0492</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>I'll cross that bridge when I come to it.</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>それはその時になったら考えます</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>I'm not worried about that yet — I'll cross that bridge when I come to it.</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>それについてはまだ心配していません。その時になったら考えます。</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>将来の問題を今から心配しすぎない、という意味の慣用句。</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>EX-0493</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Let's not get ahead of ourselves here.</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>ここでは先走らないようにしましょう</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Let's not get ahead of ourselves — we haven't even signed the contract yet.</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>先走らないようにしましょう。まだ契約書にサインもしていませんし。</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>期待や計画が先行しすぎないよう戒める表現。</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>EX-0494</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>I'll take it from here.</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>ここからは私が引き継ぎます</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Thanks for the update — I'll take it from here.</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>状況を教えてくれてありがとう、ここからは私が引き継ぎます。</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>タスクや説明を引き継ぐときの簡潔な表現。</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>EX-0495</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Let's not make a mountain out of a molehill.</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>些細なことを大げさに騒がないようにしましょう</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>It's a small typo — let's not make a mountain out of a molehill.</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>小さな誤字なので、大げさに騒がないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>些細な問題を大問題のように扱わないよう促す慣用句。</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>EX-0496</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>I'll need to loop back with my team on that.</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>その件はチームに持ち帰って確認する必要があります</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>I'll need to loop back with my team on that before I can confirm.</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>確定する前に、その件はチームに持ち帰って確認する必要があります。</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>即答を避け、社内確認を挟みたいときの定番表現。</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>EX-0497</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Let's set expectations early so there are no surprises later.</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>後で驚かないよう、早めに認識をすり合わせておきましょう</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Let's set expectations early so there are no surprises later in the project.</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>プロジェクトの後半で驚かないよう、早めに認識をすり合わせておきましょう。</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>誤解を防ぐために事前に期待値をそろえることを提案する表現。</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>EX-0498</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>I hate to pile on, but there's one more issue.</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>畳みかけるようで悪いのですが、もう一つ問題があります</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>I hate to pile on, but there's one more issue we need to discuss.</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>畳みかけるようで悪いのですが、もう一つ話し合うべき問題があります。</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>悪いニュースを重ねて伝えるときの申し訳なさを表す前置き。</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>EX-0499</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Let's keep this between us for now.</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>これは今のところここだけの話にしておきましょう</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Let's keep this between us for now until it's officially announced.</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>正式に発表されるまでは、これは今のところここだけの話にしておきましょう。</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>情報の取り扱いに注意を促す表現。</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>EX-0500</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>I don't want to rain on your parade, but have you considered the cost?</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>水を差すようで悪いのですが、コストは考慮しましたか</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>I don't want to rain on your parade, but have you considered the cost of this plan?</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>水を差すようで悪いのですが、この計画のコストは考慮しましたか。</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>相手の良いアイデアに水を差す前の申し訳なさを表す前置き表現。</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>EX-0501</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Please note that the office will observe reduced hours during the holiday season.</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>休暇シーズン中はオフィスの営業時間が短縮されますのでご了承ください</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Please note that the office will observe reduced hours during the holiday season, from December 24 to January 3.</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>12月24日から1月3日まで、休暇シーズン中はオフィスの営業時間が短縮されますのでご了承ください。</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>observe reduced hours =「短縮営業を行う」というフォーマルな表現。</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>EX-0502</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>We are currently experiencing a higher-than-usual volume of inquiries.</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>現在、通常より多くのお問い合わせをいただいております</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>We are currently experiencing a higher-than-usual volume of inquiries, so responses may be delayed.</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>現在、通常より多くのお問い合わせをいただいており、ご返信が遅れる場合がございます。</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>カスタマーサポートの自動応答でよく使われる、対応遅延を予告する表現。</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>EX-0503</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>We regret to inform you that your shipment has been delayed.</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>誠に恐縮ですが、貨物の発送が遅れていることをお知らせいたします</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>We regret to inform you that your shipment has been delayed due to a shortage of packaging materials.</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>誠に恐縮ですが、梱包資材の不足により貨物の発送が遅れていることをお知らせいたします。</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>TOEIC Part7のビジネスレターで頻出する謝罪の定型表現。</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>EX-0504</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>Please be advised that the office will be closed for renovations.</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>改装工事のため、オフィスが休業となりますのでご承知おきください</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Please be advised that the office will be closed for renovations from July 1 to July 5.</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>改装工事のため、7月1日から7月5日までオフィスが休業となりますのでご承知おきください。</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>お知らせ・通知文の冒頭でよく使われるフォーマルな定型句。</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>EX-0505</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>Kindly submit your report by the end of the business day.</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>本日の営業終了までに報告書をご提出ください</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Kindly submit your report by the end of the business day so we can review it tomorrow.</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>明日確認できるよう、本日の営業終了までに報告書をご提出ください。</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>kindlyはpleaseよりフォーマルな響きを持つ、案内文でよく使われる語。</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>EX-0506</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>We would like to bring the following matter to your attention.</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>以下の件についてご注意いただきたく存じます</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>We would like to bring the following matter to your attention regarding the upcoming audit.</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>来る監査に関する以下の件についてご注意いただきたく存じます。</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>フォーマルな通知メールの導入部で使われる定番表現。</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>EX-0507</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>This position requires a minimum of five years of relevant experience.</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>この職務には関連分野で最低5年の経験が求められます</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>This position requires a minimum of five years of relevant experience in project management.</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>この職務にはプロジェクト管理分野で最低5年の関連経験が求められます。</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>求人広告やTOEIC Part7の求人票でよく見られる表現。</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>EX-0508</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>Please retain this receipt for your records.</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>記録用としてこの領収書を保管してください</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Please retain this receipt for your records in case a refund is needed later.</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>後で返金が必要になった場合に備えて、この領収書を記録用として保管してください。</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>領収書・チケットなどに添えられる注意書きの定番表現。</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>EX-0509</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>All applicants must submit their résumés by the deadline listed below.</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>応募者は全員、下記の締め切りまでに履歴書を提出しなければなりません</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>All applicants must submit their résumés by the deadline listed below to be considered.</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>選考対象となるには、応募者は全員下記の締め切りまでに履歴書を提出しなければなりません。</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>採用案内で頻出のフォーマルな指示表現。</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>EX-0510</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>The workshop will be rescheduled due to unforeseen circumstances.</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>予期せぬ事情により、ワークショップは日程を変更いたします</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>The workshop will be rescheduled due to unforeseen circumstances; a new date will follow shortly.</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>予期せぬ事情によりワークショップは日程を変更いたします。新しい日程は追ってご連絡します。</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>予定変更を知らせるアナウンスの定型表現。</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>EX-0511</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>Please note that prices are subject to change without prior notice.</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>価格は予告なく変更される場合がございますのでご了承ください</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Please note that prices are subject to change without prior notice due to market conditions.</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>市場状況により、価格は予告なく変更される場合がございますのでご了承ください。</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>カタログや契約書でよく見られる注意書きの定型表現。</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>EX-0512</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>We are currently reviewing your application and will contact you shortly.</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>現在ご応募内容を審査中で、近日中にご連絡いたします</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>We are currently reviewing your application and will contact you shortly with next steps.</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>現在ご応募内容を審査中で、次のステップについて近日中にご連絡いたします。</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>採用選考の途中経過を伝える定番のビジネスメール表現。</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>EX-0513</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>Please ensure all fields on the form are completed accurately.</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>フォームのすべての項目を正確にご記入いただくようお願いいたします</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Please ensure all fields on the form are completed accurately before submitting.</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>提出前に、フォームのすべての項目を正確にご記入いただくようお願いいたします。</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>申込書・フォームの案内でよく使われる指示表現。</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>EX-0514</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>The meeting has been moved up to accommodate the client's schedule.</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>クライアントのスケジュールに合わせて会議が前倒しになりました</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>The meeting has been moved up to accommodate the client's schedule; it now starts at 9 a.m.</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>クライアントのスケジュールに合わせて会議が前倒しになり、午前9時開始となりました。</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>move up =「（予定を）前倒しにする」というビジネス頻出表現。</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>EX-0515</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>We appreciate your patience while we resolve this issue.</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>この問題を解決するまでの間、ご辛抱いただきありがとうございます</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>We appreciate your patience while we resolve this issue with your account.</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>お客様のアカウントに関するこの問題を解決するまでの間、ご辛抱いただきありがとうございます。</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>トラブル対応中に顧客へ送る定番の感謝・お詫び表現。</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>EX-0516</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>The attached document outlines the terms and conditions in detail.</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>添付の書類に諸条件を詳しく記載しております</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>The attached document outlines the terms and conditions in detail, so please review it carefully.</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>添付の書類に諸条件を詳しく記載しておりますので、よくご確認ください。</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>契約書類の送付時に使われる定型のビジネス表現。</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>EX-0517</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>Please allow up to two business days for a response.</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>ご返信までに最大2営業日ほどいただく場合がございます</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Please allow up to two business days for a response from our support team.</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>サポートチームからのご返信までに最大2営業日ほどいただく場合がございます。</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>問い合わせフォームや自動返信メールでよく見られる表現。</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>EX-0518</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>The seminar is open to all employees regardless of department.</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>このセミナーは部署を問わず全従業員が参加可能です</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>The seminar is open to all employees regardless of department or job title.</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>このセミナーは部署や役職を問わず全従業員が参加可能です。</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>社内案内でよく使われる「規制・条件がない」ことを示す表現。</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>EX-0519</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>Due to high demand, please expect a slight delay in shipping.</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>需要が高いため、配送に若干の遅れが生じる可能性がございます</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Due to high demand, please expect a slight delay in shipping this month.</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>今月は需要が高いため、配送に若干の遅れが生じる可能性がございます。</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>注文確認メールなどで見られる遅延予告の定番表現。</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>EX-0520</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>We look forward to welcoming you to our team.</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>私たちのチームにお迎えできることを楽しみにしております</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>We look forward to welcoming you to our team starting next Monday.</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>来週月曜日から、私たちのチームにお迎えできることを楽しみにしております。</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>内定通知や入社案内で使われる歓迎の定型表現。</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>EX-0521</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>Please do not reply to this automated message.</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>この自動送信メールには返信しないでください</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Please do not reply to this automated message; contact support instead.</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>この自動送信メールには返信せず、サポートまでご連絡ください。</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>自動返信メールの末尾に頻出する注意書き。</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>EX-0522</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>The revised itinerary will be sent to all attendees shortly.</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>改訂版の行程表は近日中に参加者全員へお送りします</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>The revised itinerary will be sent to all attendees shortly after confirmation.</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>確定後、改訂版の行程表は近日中に参加者全員へお送りします。</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>出張・イベントの行程表送付でよく使われる表現。</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>EX-0523</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>This offer is valid while supplies last.</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>このオファーは在庫がなくなり次第終了となります</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>This offer is valid while supplies last, so please order soon.</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>このオファーは在庫がなくなり次第終了となりますので、お早めにご注文ください。</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>販促メールやチラシで頻出の在庫限定を示す表現。</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>EX-0524</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>Employees are encouraged to submit feedback through the online portal.</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>従業員はオンラインポータルを通じてフィードバックを提出することが推奨されています</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Employees are encouraged to submit feedback through the online portal by Friday.</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>従業員は金曜日までにオンラインポータルを通じてフィードバックを提出することが推奨されています。</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>be encouraged to ~は「〜することが推奨される」という柔らかい指示表現。</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>EX-0525</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>Please direct any inquiries to the customer service department.</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>お問い合わせはすべてカスタマーサービス部門までお願いいたします</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Please direct any inquiries to the customer service department at the number below.</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>お問い合わせは下記番号のカスタマーサービス部門までお願いいたします。</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>案内文の末尾でよく使われる問い合わせ先の指示表現。</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>EX-0526</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>The company reserves the right to modify this policy at any time.</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>当社はこの方針をいつでも変更する権利を有します</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>The company reserves the right to modify this policy at any time without notice.</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>当社はこの方針を予告なくいつでも変更する権利を有します。</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>規約や社内方針文書で頻出のフォーマルな法的表現。</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>EX-0527</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>Thank you for your continued patronage.</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>日頃のご愛顧に感謝申し上げます</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Thank you for your continued patronage over the past ten years.</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>この10年間の日頃のご愛顧に感謝申し上げます。</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>顧客への感謝を示すフォーマルなビジネスレターの定型句。</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>EX-0528</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>We sincerely apologize for any inconvenience this may have caused.</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>ご不便をおかけしましたこと、心よりお詫び申し上げます</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>We sincerely apologize for any inconvenience this delay may have caused.</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>この遅延によりご不便をおかけしましたこと、心よりお詫び申し上げます。</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>apologies for any inconvenienceよりさらにフォーマルな謝罪表現。</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>EX-0529</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>Please arrive at least fifteen minutes prior to the scheduled start time.</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>予定開始時刻の少なくとも15分前にはお越しください</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Please arrive at least fifteen minutes prior to the scheduled start time for registration.</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>受付のため、予定開始時刻の少なくとも15分前にはお越しください。</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>イベント・セミナー案内でよく見られる時間指定の表現。</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>EX-0530</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>The board has approved the proposed budget for the next fiscal year.</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>取締役会は来年度の予算案を承認しました</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>The board has approved the proposed budget for the next fiscal year at today's meeting.</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>本日の会議で、取締役会は来年度の予算案を承認しました。</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>TOEIC Part7の社内報告書でよく登場する決定事項の表現。</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>EX-0531</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>Please make sure your badge is visible at all times while on the premises.</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>構内にいる間は常に社員証を見える位置に着用してください</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Please make sure your badge is visible at all times while on the premises for security reasons.</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>セキュリティ上の理由により、構内にいる間は常に社員証を見える位置に着用してください。</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>入館案内やセキュリティポリシーで頻出の指示表現。</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>EX-0532</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>The new branch is expected to open its doors early next year.</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>新支店は来年初めに開業する見込みです</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>The new branch is expected to open its doors early next year, pending final approval.</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>最終承認待ちですが、新支店は来年初めに開業する見込みです。</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>open its doors =「開業する」という比喩的な表現。TOEICの記事問題で頻出。</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>EX-0533</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>メール,プレゼン</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>We are pleased to announce the launch of our new product line.</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>新しい製品ラインの発売を発表できることを嬉しく思います</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>We are pleased to announce the launch of our new product line this fall.</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>この秋、新しい製品ラインの発売を発表できることを嬉しく思います。</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>プレスリリースや社内発表でよく使われる前向きな告知表現。</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>EX-0534</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>Kindly disregard the previous email if you have already responded.</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>すでにご返信いただいている場合は、前回のメールは無視してください</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Kindly disregard the previous email if you have already responded to our request.</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>すでに私どもの依頼にご返信いただいている場合は、前回のメールは無視してください。</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>メールの行き違いを整理する際に使うフォーマルな表現。</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>EX-0535</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>The deadline has been extended to accommodate additional applicants.</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>応募者を増やすため、締め切りが延長されました</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>The deadline has been extended to accommodate additional applicants who requested more time.</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>もっと時間が欲しいと要望した応募者に対応するため、締め切りが延長されました。</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>締め切り延長の理由を説明する定番の表現。</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>EX-0536</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>Please be aware that seating is limited and available on a first-come, first-served basis.</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>座席には限りがあり、先着順となりますのでご了承ください</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Please be aware that seating is limited and available on a first-come, first-served basis.</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>座席には限りがあり、先着順となりますのでご了承ください。</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>イベント案内で頻出の「先着順」を表す定型表現。</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>EX-0537</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>All participants will receive a certificate upon completion of the course.</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>講座修了時に、参加者全員に修了証が授与されます</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>All participants will receive a certificate upon completion of the course.</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>講座修了時に、参加者全員に修了証が授与されます。</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>研修・講座の案内文でよく使われる表現。</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>EX-0538</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>We would like to express our sincere gratitude for your continued support.</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>日頃のご支援に心より感謝申し上げます</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>We would like to express our sincere gratitude for your continued support throughout the year.</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>一年を通じての日頃のご支援に心より感謝申し上げます。</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>年末挨拶や取引先への礼状で使われる非常にフォーマルな表現。</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>EX-0539</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>Please confirm your attendance by replying to this email.</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>このメールに返信して出席の可否をご確認ください</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Please confirm your attendance by replying to this email no later than Friday.</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>金曜日までにこのメールに返信して出席の可否をご確認ください。</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>招待メールの締めくくりで頻出のRSVP依頼表現。</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>EX-0540</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>The facility will undergo maintenance over the weekend.</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>週末にかけて施設のメンテナンスが行われます</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>The facility will undergo maintenance over the weekend, so access will be limited.</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>週末にかけて施設のメンテナンスが行われるため、利用が制限されます。</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>undergo maintenance =「メンテナンスを受ける」という頻出の表現。</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>EX-0541</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>Our records indicate that your subscription is due for renewal.</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>記録によりますと、お客様のご契約は更新時期を迎えております</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Our records indicate that your subscription is due for renewal next month.</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>記録によりますと、お客様のご契約は来月更新時期を迎えております。</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>契約更新の案内メールで頻出のフォーマルな表現。</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>EX-0542</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>メール,交渉</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>The vendor has agreed to honor the original quote despite the price increase.</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>値上げにもかかわらず、業者は当初の見積もりを尊重することに同意しました</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>The vendor has agreed to honor the original quote despite the recent price increase.</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>最近の値上げにもかかわらず、業者は当初の見積もりを尊重することに同意しました。</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>honor a quote =「見積もりを守る、その条件通りに応じる」という頻出表現。</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>EX-0543</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>Please refrain from using personal devices during the training session.</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>研修中は私用の端末の使用をお控えください</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Please refrain from using personal devices during the training session.</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>研修中は私用の端末の使用をお控えください。</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>refrain from ~ing =「〜を控える」という丁寧な禁止表現。</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>EX-0544</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>The updated handbook is now available on the internal website.</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>更新版のハンドブックは社内サイトでご覧いただけます</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>The updated handbook is now available on the internal website for all staff.</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>更新版のハンドブックは全スタッフ向けに社内サイトでご覧いただけます。</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>社内通知でよく使われる更新情報の案内表現。</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>EX-0545</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>We regret that we are unable to process your request at this time.</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>誠に恐縮ですが、現時点ではご要望にお応えすることができません</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>We regret that we are unable to process your request at this time due to system maintenance.</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>システムメンテナンスのため、誠に恐縮ですが現時点ではご要望にお応えすることができません。</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>丁寧に依頼を断る際のフォーマルな定型表現。</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>EX-0546</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>Please note that all times listed are in local time.</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>記載されている時刻はすべて現地時間となりますのでご注意ください</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Please note that all times listed are in local time unless otherwise specified.</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>特に断りがない限り、記載されている時刻はすべて現地時間となりますのでご注意ください。</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>国際的なやり取りで時差の誤解を防ぐための注意書き。</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>EX-0547</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>The company is committed to providing a safe working environment for all staff.</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>当社は全スタッフに安全な職場環境を提供することに尽力しています</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>The company is committed to providing a safe working environment for all staff members.</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>当社は全スタッフに安全な職場環境を提供することに尽力しています。</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>be committed to ~ing =「〜することに尽力する」という頻出のフォーマル表現。</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>EX-0548</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Kindly review the attached invoice and remit payment at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>添付の請求書をご確認の上、できるだけ早くお支払いください</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Kindly review the attached invoice and remit payment at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>添付の請求書をご確認の上、できるだけ早くお支払いください。</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>remit payment =「支払いを送金する」というフォーマルな会計表現。</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>EX-0549</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>The results of the survey will be shared with all participants next month.</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>アンケート結果は来月、参加者全員に共有される予定です</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>The results of the survey will be shared with all participants next month.</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>アンケート結果は来月、参加者全員に共有される予定です。</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>アンケート結果の共有について伝える定番の告知表現。</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>EX-0550</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>We kindly ask that you review the enclosed agreement before signing.</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>署名する前に、同封の契約書をご確認いただきますようお願い申し上げます</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>We kindly ask that you review the enclosed agreement before signing and returning it.</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>署名して返送する前に、同封の契約書をご確認いただきますようお願い申し上げます。</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>契約書送付時に添える非常に丁寧な依頼表現。</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S551" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
